--- a/resumen_trabajos_1.xlsx
+++ b/resumen_trabajos_1.xlsx
@@ -8,24 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dacm/we/odoo_con_trabajos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C335D6-A67A-514A-B5D5-D2BEC30C6BD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA42FCF1-A245-1D4E-BC71-CC4960E3C1BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="20400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="36220" yWindow="-4820" windowWidth="33600" windowHeight="19320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja2" sheetId="3" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
-    <sheet name="Hoja1" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$A$1:$N$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$49</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="194">
   <si>
     <t>OT</t>
   </si>
@@ -105,88 +103,19 @@
 Pozo aún se encuentra en periodo de mantenimiento.</t>
   </si>
   <si>
-    <t>Elías Sanchez</t>
-  </si>
-  <si>
-    <t>Inspección, validación SMA</t>
-  </si>
-  <si>
-    <t>Global Tórtolas</t>
-  </si>
-  <si>
-    <t>[Global Tórtolas] Pozo Dren ME Nodo</t>
+    <t>Matías Pomar</t>
+  </si>
+  <si>
+    <t>Levantamiento tecnico nuevo punto</t>
+  </si>
+  <si>
+    <t>Farellones</t>
+  </si>
+  <si>
+    <t>[Farellones] Planta de Tratamiento</t>
   </si>
   <si>
     <t>LT</t>
-  </si>
-  <si>
-    <t>03/12/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patricio Cortés </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se realiza levantamiento de instrumentación en Dren Me, buscando comprobar siesque se lee el flujo del agua. Visualizando medidores de PH, Temperatura, turbidez en el punto. 
-Hay dos niveles de caída de agua en el dren.
-Dren: 2 metros de ancho 7 metros aprox de largo desde llegada de tuberías hasta fin del dren.
-Se debe proponer método de medición. </t>
-  </si>
-  <si>
-    <t>[Global Tórtolas] Pozo PP-31C</t>
-  </si>
-  <si>
-    <t>Se registra el valor de profundidad del pozo hasta el espejo de agua siendo de 73 metros
-Los valores obtenidos se informan a área de automatización para reflejarlo en plataforma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Levantamiento - Cambio de tarjeta SIM. </t>
-  </si>
-  <si>
-    <t>[Gestión Hídrica El Soldado] Estero El Sauce</t>
-  </si>
-  <si>
-    <t>04/12/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Superintendencia de recursos hidricos </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se realiza levantamiento en terreno para observar el procedimiento del montaje de equipo RQ30 junto al prevencionista de riesgo.
-Se observan 22m lineales de canalización  desde equipo hasta cruce de tubería y luego 15m hasta donde estará ubicado el poste.
-Se debe coordinar con personal de SS el procedimiento. </t>
-  </si>
-  <si>
-    <t>[Gestión Hídrica El Soldado] Caudalimetros HDS Sector Planta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se reemplazan tarjetas SD de raspberry para obtener datos de telemetria. 
-Las tarjetas de visualizaran el viernes con equipo de automatización.
-El punto se encontraba desenergizado asique se debe verificar funcionamiento correcto cuando vuelva a estar operativo
-Se designan los tableros con código qr correspondiente para tener la exactitud de lo implementado.
-</t>
-  </si>
-  <si>
-    <t>[Gestión Hídrica El Soldado] Lora Dren los Caleos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se reemplazan tarjetas SD de raspberry para obtener datos de telemetria. 
-Se verifica funcionamiento con equipo de automatización para poder dejar transmitiendo y obteniendo lecturas de manera correcta en el punto
-Observaciones
-Muchos insectos (panales)
-Tablero solar se encuentra desconectado
-No se logra identificar tableros ya que no correspondía la designación asignada. </t>
-  </si>
-  <si>
-    <t>Matías Pomar</t>
-  </si>
-  <si>
-    <t>Levantamiento tecnico nuevo punto</t>
-  </si>
-  <si>
-    <t>Farellones</t>
-  </si>
-  <si>
-    <t>[Farellones] Planta de Tratamiento</t>
   </si>
   <si>
     <t>26/11/2025</t>
@@ -201,6 +130,9 @@
 Adicionalmente, se incorporará un switch de comunicaciones que será instalado en la Planta de Tratamiento de Farellones para integrar los equipos LoRa. También se deben considerar los cables y suministros necesarios para el conexionado de los equipos.</t>
   </si>
   <si>
+    <t>Elías Sanchez</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mantenimiento preventivo </t>
   </si>
   <si>
@@ -208,6 +140,9 @@
   </si>
   <si>
     <t>05/12/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Superintendencia de recursos hidricos </t>
   </si>
   <si>
     <t xml:space="preserve">43 mts esta instalado el sensor hidrostatico 
@@ -565,6 +500,9 @@
     <t>Implementacion BN12</t>
   </si>
   <si>
+    <t>Global Tórtolas</t>
+  </si>
+  <si>
     <t>[Global Tórtolas] Pozo BN12</t>
   </si>
   <si>
@@ -605,6 +543,26 @@
   </si>
   <si>
     <t xml:space="preserve">Se procede ir al punto para revisión e inspección visual en compañía de don Nicolas Valenzuela,  lo que provoca fallas de medición es la ventosa del lugar que se encuentra restringida su válvula, además se procede a realizar reemplazo de tarjeta SD del tablero. </t>
+  </si>
+  <si>
+    <t>[Gestión Hídrica El Soldado] PM-3 Nodo B19</t>
+  </si>
+  <si>
+    <t>01/01/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por aviso de oficina procedemos ir al punto a recetear el tablero ya que se encontraba la sonda dando datos erróneo. </t>
+  </si>
+  <si>
+    <t>Pozos monitoreo exteriores y ET 0F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se realizo inspección visual de cada punto para que no se encontrarán bandalizado o con algún problema. </t>
+  </si>
+  <si>
+    <t>Se da revisión al punto por que ese encontraba caído y dando datos erróneos la sonda. 
+Se deja sonda con agua ya que se encontraba sin agua.
+Válvula estaba abierta. Habían indicios qué el agua había corrido por el piso hacia el exterior.</t>
   </si>
   <si>
     <t>Ángel Zamora</t>
@@ -1117,24 +1075,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C7B82D1-E4AC-A348-94B9-B1A96983A903}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="15.83203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="5" max="5" width="54.5" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -1182,7 +1125,7 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B2" t="s">
         <v>25</v>
@@ -1214,31 +1157,31 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J3">
         <v>5</v>
@@ -1246,31 +1189,31 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
         <v>22</v>
       </c>
       <c r="E4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" t="s">
         <v>36</v>
       </c>
-      <c r="F4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>37</v>
       </c>
-      <c r="H4" t="s">
-        <v>38</v>
-      </c>
       <c r="I4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -1278,31 +1221,31 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
       </c>
       <c r="G5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="I5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J5">
         <v>5</v>
@@ -1310,31 +1253,31 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
       </c>
       <c r="G6" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="H6" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="I6" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="J6">
         <v>5</v>
@@ -1342,31 +1285,31 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="G7" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="H7" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="I7" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="J7">
         <v>5</v>
@@ -1374,31 +1317,31 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" t="s">
         <v>51</v>
       </c>
-      <c r="D8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="I8" t="s">
         <v>52</v>
-      </c>
-      <c r="F8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H8" t="s">
-        <v>38</v>
-      </c>
-      <c r="I8" t="s">
-        <v>54</v>
       </c>
       <c r="J8">
         <v>5</v>
@@ -1406,63 +1349,75 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>152</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>132</v>
       </c>
       <c r="E9" t="s">
-        <v>55</v>
+        <v>153</v>
       </c>
       <c r="F9" t="s">
-        <v>18</v>
+        <v>154</v>
       </c>
       <c r="G9" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="H9" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="I9" t="s">
-        <v>56</v>
+        <v>155</v>
       </c>
       <c r="J9">
         <v>5</v>
+      </c>
+      <c r="K9" t="s">
+        <v>156</v>
+      </c>
+      <c r="L9" t="s">
+        <v>157</v>
+      </c>
+      <c r="M9" t="s">
+        <v>158</v>
+      </c>
+      <c r="N9" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E10" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
       </c>
       <c r="G10" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H10" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="I10" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="J10">
         <v>5</v>
@@ -1470,31 +1425,31 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
       </c>
       <c r="G11" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="H11" t="s">
         <v>20</v>
       </c>
       <c r="I11" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="J11">
         <v>5</v>
@@ -1502,139 +1457,163 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="D12" t="s">
         <v>22</v>
       </c>
       <c r="E12" t="s">
-        <v>23</v>
+        <v>160</v>
       </c>
       <c r="F12" t="s">
-        <v>18</v>
+        <v>161</v>
       </c>
       <c r="G12" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="H12" t="s">
         <v>20</v>
       </c>
       <c r="I12" t="s">
-        <v>24</v>
+        <v>162</v>
       </c>
       <c r="J12">
         <v>5</v>
+      </c>
+      <c r="K12" t="s">
+        <v>163</v>
+      </c>
+      <c r="L12" t="s">
+        <v>164</v>
+      </c>
+      <c r="M12" t="s">
+        <v>165</v>
+      </c>
+      <c r="N12" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="E13" t="s">
-        <v>66</v>
+        <v>160</v>
       </c>
       <c r="F13" t="s">
-        <v>29</v>
+        <v>161</v>
       </c>
       <c r="G13" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H13" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="I13" t="s">
-        <v>68</v>
+        <v>162</v>
       </c>
       <c r="J13">
         <v>5</v>
+      </c>
+      <c r="K13" t="s">
+        <v>167</v>
+      </c>
+      <c r="L13" t="s">
+        <v>168</v>
+      </c>
+      <c r="M13" t="s">
+        <v>169</v>
+      </c>
+      <c r="N13" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" t="s">
+        <v>160</v>
+      </c>
+      <c r="F14" t="s">
         <v>161</v>
       </c>
-      <c r="C14" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="G14" t="s">
+        <v>55</v>
+      </c>
+      <c r="H14" t="s">
+        <v>20</v>
+      </c>
+      <c r="I14" t="s">
         <v>162</v>
       </c>
-      <c r="F14" t="s">
-        <v>163</v>
-      </c>
-      <c r="G14" t="s">
-        <v>60</v>
-      </c>
-      <c r="H14" t="s">
-        <v>61</v>
-      </c>
-      <c r="I14" t="s">
-        <v>164</v>
-      </c>
       <c r="J14">
         <v>5</v>
       </c>
       <c r="K14" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="L14" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="M14" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="N14" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
       </c>
       <c r="G15" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="H15" t="s">
+        <v>37</v>
+      </c>
+      <c r="I15" t="s">
         <v>61</v>
-      </c>
-      <c r="I15" t="s">
-        <v>72</v>
       </c>
       <c r="J15">
         <v>5</v>
@@ -1642,31 +1621,31 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="D16" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="E16" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
       </c>
       <c r="G16" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="H16" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="I16" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="J16">
         <v>5</v>
@@ -1674,163 +1653,139 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>152</v>
       </c>
       <c r="C17" t="s">
-        <v>73</v>
+        <v>174</v>
       </c>
       <c r="D17" t="s">
         <v>22</v>
       </c>
       <c r="E17" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="F17" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="G17" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="H17" t="s">
-        <v>20</v>
+        <v>176</v>
       </c>
       <c r="I17" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="J17">
         <v>5</v>
       </c>
       <c r="K17" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="L17" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="M17" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="N17" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B18" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="C18" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D18" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="E18" t="s">
-        <v>169</v>
+        <v>54</v>
       </c>
       <c r="F18" t="s">
-        <v>170</v>
+        <v>18</v>
       </c>
       <c r="G18" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="H18" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="I18" t="s">
-        <v>171</v>
+        <v>68</v>
       </c>
       <c r="J18">
         <v>5</v>
-      </c>
-      <c r="K18" t="s">
-        <v>176</v>
-      </c>
-      <c r="L18" t="s">
-        <v>177</v>
-      </c>
-      <c r="M18" t="s">
-        <v>178</v>
-      </c>
-      <c r="N18" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="B19" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C19" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D19" t="s">
         <v>22</v>
       </c>
       <c r="E19" t="s">
-        <v>169</v>
+        <v>70</v>
       </c>
       <c r="F19" t="s">
-        <v>170</v>
+        <v>18</v>
       </c>
       <c r="G19" t="s">
         <v>71</v>
       </c>
       <c r="H19" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="I19" t="s">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="J19">
         <v>5</v>
-      </c>
-      <c r="K19" t="s">
-        <v>165</v>
-      </c>
-      <c r="L19" t="s">
-        <v>180</v>
-      </c>
-      <c r="M19" t="s">
-        <v>181</v>
-      </c>
-      <c r="N19" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="C20" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" t="s">
+        <v>54</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" t="s">
+        <v>74</v>
+      </c>
+      <c r="H20" t="s">
+        <v>45</v>
+      </c>
+      <c r="I20" t="s">
         <v>75</v>
-      </c>
-      <c r="D20" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20" t="s">
-        <v>76</v>
-      </c>
-      <c r="F20" t="s">
-        <v>18</v>
-      </c>
-      <c r="G20" t="s">
-        <v>53</v>
-      </c>
-      <c r="H20" t="s">
-        <v>38</v>
-      </c>
-      <c r="I20" t="s">
-        <v>77</v>
       </c>
       <c r="J20">
         <v>5</v>
@@ -1838,107 +1793,107 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="B21" t="s">
-        <v>25</v>
+        <v>152</v>
       </c>
       <c r="C21" t="s">
-        <v>75</v>
+        <v>181</v>
       </c>
       <c r="D21" t="s">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="E21" t="s">
-        <v>79</v>
+        <v>182</v>
       </c>
       <c r="F21" t="s">
-        <v>18</v>
+        <v>183</v>
       </c>
       <c r="G21" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="I21" t="s">
-        <v>80</v>
+        <v>184</v>
       </c>
       <c r="J21">
         <v>5</v>
+      </c>
+      <c r="K21" t="s">
+        <v>178</v>
+      </c>
+      <c r="L21" t="s">
+        <v>165</v>
+      </c>
+      <c r="M21" t="s">
+        <v>165</v>
+      </c>
+      <c r="N21" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="B22" t="s">
-        <v>161</v>
+        <v>33</v>
       </c>
       <c r="C22" t="s">
-        <v>183</v>
+        <v>76</v>
       </c>
       <c r="D22" t="s">
         <v>22</v>
       </c>
       <c r="E22" t="s">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="F22" t="s">
-        <v>170</v>
+        <v>18</v>
       </c>
       <c r="G22" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H22" t="s">
-        <v>185</v>
+        <v>37</v>
       </c>
       <c r="I22" t="s">
-        <v>186</v>
+        <v>78</v>
       </c>
       <c r="J22">
         <v>5</v>
-      </c>
-      <c r="K22" t="s">
-        <v>187</v>
-      </c>
-      <c r="L22" t="s">
-        <v>188</v>
-      </c>
-      <c r="M22" t="s">
-        <v>189</v>
-      </c>
-      <c r="N22" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="B23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" t="s">
+        <v>80</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
         <v>81</v>
       </c>
-      <c r="C23" t="s">
+      <c r="H23" t="s">
+        <v>37</v>
+      </c>
+      <c r="I23" t="s">
         <v>82</v>
-      </c>
-      <c r="D23" t="s">
-        <v>58</v>
-      </c>
-      <c r="E23" t="s">
-        <v>70</v>
-      </c>
-      <c r="F23" t="s">
-        <v>18</v>
-      </c>
-      <c r="G23" t="s">
-        <v>71</v>
-      </c>
-      <c r="H23" t="s">
-        <v>83</v>
-      </c>
-      <c r="I23" t="s">
-        <v>84</v>
       </c>
       <c r="J23">
         <v>5</v>
@@ -1946,31 +1901,31 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C24" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D24" t="s">
         <v>22</v>
       </c>
       <c r="E24" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F24" t="s">
         <v>18</v>
       </c>
       <c r="G24" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I24" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J24">
         <v>5</v>
@@ -1978,31 +1933,31 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B25" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" t="s">
+        <v>85</v>
+      </c>
+      <c r="D25" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" t="s">
+        <v>54</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" t="s">
         <v>81</v>
       </c>
-      <c r="C25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D25" t="s">
-        <v>58</v>
-      </c>
-      <c r="E25" t="s">
-        <v>70</v>
-      </c>
-      <c r="F25" t="s">
-        <v>18</v>
-      </c>
-      <c r="G25" t="s">
-        <v>90</v>
-      </c>
       <c r="H25" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="I25" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="J25">
         <v>5</v>
@@ -2010,75 +1965,63 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B26" t="s">
-        <v>161</v>
+        <v>65</v>
       </c>
       <c r="C26" t="s">
-        <v>190</v>
+        <v>87</v>
       </c>
       <c r="D26" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E26" t="s">
-        <v>191</v>
+        <v>54</v>
       </c>
       <c r="F26" t="s">
-        <v>192</v>
+        <v>18</v>
       </c>
       <c r="G26" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="I26" t="s">
-        <v>193</v>
+        <v>89</v>
       </c>
       <c r="J26">
         <v>5</v>
-      </c>
-      <c r="K26" t="s">
-        <v>187</v>
-      </c>
-      <c r="L26" t="s">
-        <v>174</v>
-      </c>
-      <c r="M26" t="s">
-        <v>174</v>
-      </c>
-      <c r="N26" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B27" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D27" t="s">
         <v>22</v>
       </c>
       <c r="E27" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="F27" t="s">
         <v>18</v>
       </c>
       <c r="G27" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I27" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J27">
         <v>5</v>
@@ -2086,31 +2029,31 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B28" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C28" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D28" t="s">
         <v>22</v>
       </c>
       <c r="E28" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F28" t="s">
         <v>18</v>
       </c>
       <c r="G28" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="H28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I28" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="J28">
         <v>5</v>
@@ -2118,31 +2061,31 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B29" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D29" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="E29" t="s">
+        <v>98</v>
+      </c>
+      <c r="F29" t="s">
         <v>99</v>
       </c>
-      <c r="F29" t="s">
-        <v>18</v>
-      </c>
       <c r="G29" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H29" t="s">
-        <v>38</v>
+        <v>101</v>
       </c>
       <c r="I29" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J29">
         <v>5</v>
@@ -2150,31 +2093,31 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B30" t="s">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="C30" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D30" t="s">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="E30" t="s">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="F30" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="G30" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="H30" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="I30" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="J30">
         <v>5</v>
@@ -2182,31 +2125,31 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B31" t="s">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="C31" t="s">
         <v>103</v>
       </c>
       <c r="D31" t="s">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="E31" t="s">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="F31" t="s">
         <v>18</v>
       </c>
       <c r="G31" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H31" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="I31" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J31">
         <v>5</v>
@@ -2214,31 +2157,31 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="C32" t="s">
-        <v>106</v>
+        <v>34</v>
       </c>
       <c r="D32" t="s">
         <v>22</v>
       </c>
       <c r="E32" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="F32" t="s">
         <v>18</v>
       </c>
       <c r="G32" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="H32" t="s">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="I32" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="J32">
         <v>5</v>
@@ -2246,31 +2189,31 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="B33" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="C33" t="s">
+        <v>112</v>
+      </c>
+      <c r="D33" t="s">
+        <v>113</v>
+      </c>
+      <c r="E33" t="s">
+        <v>114</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" t="s">
         <v>106</v>
       </c>
-      <c r="D33" t="s">
-        <v>22</v>
-      </c>
-      <c r="E33" t="s">
-        <v>109</v>
-      </c>
-      <c r="F33" t="s">
-        <v>18</v>
-      </c>
-      <c r="G33" t="s">
-        <v>107</v>
-      </c>
       <c r="H33" t="s">
-        <v>38</v>
+        <v>115</v>
       </c>
       <c r="I33" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="J33">
         <v>5</v>
@@ -2278,31 +2221,31 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="B34" t="s">
-        <v>111</v>
+        <v>65</v>
       </c>
       <c r="C34" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D34" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E34" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F34" t="s">
-        <v>115</v>
+        <v>18</v>
       </c>
       <c r="G34" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="H34" t="s">
-        <v>117</v>
+        <v>45</v>
       </c>
       <c r="I34" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J34">
         <v>5</v>
@@ -2310,13 +2253,13 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="B35" t="s">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="C35" t="s">
-        <v>119</v>
+        <v>34</v>
       </c>
       <c r="D35" t="s">
         <v>120</v>
@@ -2325,16 +2268,16 @@
         <v>121</v>
       </c>
       <c r="F35" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="G35" t="s">
+        <v>106</v>
+      </c>
+      <c r="H35" t="s">
+        <v>110</v>
+      </c>
+      <c r="I35" t="s">
         <v>122</v>
-      </c>
-      <c r="H35" t="s">
-        <v>61</v>
-      </c>
-      <c r="I35" t="s">
-        <v>123</v>
       </c>
       <c r="J35">
         <v>5</v>
@@ -2342,31 +2285,31 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="B36" t="s">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="C36" t="s">
-        <v>119</v>
+        <v>34</v>
       </c>
       <c r="D36" t="s">
-        <v>120</v>
+        <v>22</v>
       </c>
       <c r="E36" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F36" t="s">
         <v>18</v>
       </c>
       <c r="G36" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="H36" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="I36" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J36">
         <v>5</v>
@@ -2374,13 +2317,13 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="B37" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="C37" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D37" t="s">
         <v>22</v>
@@ -2392,10 +2335,10 @@
         <v>18</v>
       </c>
       <c r="G37" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="H37" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="I37" t="s">
         <v>127</v>
@@ -2406,31 +2349,31 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="B38" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D38" t="s">
+        <v>120</v>
+      </c>
+      <c r="E38" t="s">
         <v>128</v>
       </c>
-      <c r="D38" t="s">
+      <c r="F38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" t="s">
         <v>129</v>
       </c>
-      <c r="E38" t="s">
+      <c r="H38" t="s">
+        <v>110</v>
+      </c>
+      <c r="I38" t="s">
         <v>130</v>
-      </c>
-      <c r="F38" t="s">
-        <v>18</v>
-      </c>
-      <c r="G38" t="s">
-        <v>122</v>
-      </c>
-      <c r="H38" t="s">
-        <v>131</v>
-      </c>
-      <c r="I38" t="s">
-        <v>132</v>
       </c>
       <c r="J38">
         <v>5</v>
@@ -2438,28 +2381,28 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="B39" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="C39" t="s">
+        <v>131</v>
+      </c>
+      <c r="D39" t="s">
+        <v>132</v>
+      </c>
+      <c r="E39" t="s">
         <v>133</v>
       </c>
-      <c r="D39" t="s">
-        <v>121</v>
-      </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" t="s">
         <v>134</v>
       </c>
-      <c r="F39" t="s">
-        <v>18</v>
-      </c>
-      <c r="G39" t="s">
-        <v>122</v>
-      </c>
       <c r="H39" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="I39" t="s">
         <v>135</v>
@@ -2470,28 +2413,28 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B40" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="C40" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D40" t="s">
+        <v>120</v>
+      </c>
+      <c r="E40" t="s">
         <v>136</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" t="s">
         <v>137</v>
       </c>
-      <c r="F40" t="s">
-        <v>18</v>
-      </c>
-      <c r="G40" t="s">
-        <v>122</v>
-      </c>
       <c r="H40" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="I40" t="s">
         <v>138</v>
@@ -2502,31 +2445,31 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B41" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="C41" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D41" t="s">
         <v>22</v>
       </c>
       <c r="E41" t="s">
+        <v>125</v>
+      </c>
+      <c r="F41" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" t="s">
+        <v>137</v>
+      </c>
+      <c r="H41" t="s">
+        <v>110</v>
+      </c>
+      <c r="I41" t="s">
         <v>139</v>
-      </c>
-      <c r="F41" t="s">
-        <v>18</v>
-      </c>
-      <c r="G41" t="s">
-        <v>122</v>
-      </c>
-      <c r="H41" t="s">
-        <v>126</v>
-      </c>
-      <c r="I41" t="s">
-        <v>140</v>
       </c>
       <c r="J41">
         <v>5</v>
@@ -2534,31 +2477,31 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B42" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="C42" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D42" t="s">
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="E42" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F42" t="s">
         <v>18</v>
       </c>
       <c r="G42" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="H42" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="I42" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="J42">
         <v>5</v>
@@ -2566,63 +2509,75 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B43" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="C43" t="s">
-        <v>51</v>
+        <v>185</v>
       </c>
       <c r="D43" t="s">
-        <v>136</v>
+        <v>186</v>
       </c>
       <c r="E43" t="s">
-        <v>144</v>
+        <v>187</v>
       </c>
       <c r="F43" t="s">
-        <v>18</v>
+        <v>183</v>
       </c>
       <c r="G43" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="H43" t="s">
-        <v>126</v>
+        <v>188</v>
       </c>
       <c r="I43" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="J43">
         <v>5</v>
+      </c>
+      <c r="K43" t="s">
+        <v>178</v>
+      </c>
+      <c r="L43" t="s">
+        <v>165</v>
+      </c>
+      <c r="M43" t="s">
+        <v>165</v>
+      </c>
+      <c r="N43" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="B44" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="C44" t="s">
-        <v>147</v>
+        <v>34</v>
       </c>
       <c r="D44" t="s">
-        <v>27</v>
+        <v>120</v>
       </c>
       <c r="E44" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="F44" t="s">
         <v>18</v>
       </c>
       <c r="G44" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="H44" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="I44" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="J44">
         <v>5</v>
@@ -2630,31 +2585,31 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B45" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="C45" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D45" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="E45" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="F45" t="s">
         <v>18</v>
       </c>
       <c r="G45" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="H45" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="I45" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="J45">
         <v>5</v>
@@ -2662,63 +2617,75 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="B46" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="C46" t="s">
-        <v>51</v>
+        <v>191</v>
       </c>
       <c r="D46" t="s">
-        <v>22</v>
+        <v>186</v>
       </c>
       <c r="E46" t="s">
+        <v>187</v>
+      </c>
+      <c r="F46" t="s">
+        <v>183</v>
+      </c>
+      <c r="G46" t="s">
         <v>141</v>
       </c>
-      <c r="F46" t="s">
-        <v>18</v>
-      </c>
-      <c r="G46" t="s">
-        <v>152</v>
-      </c>
       <c r="H46" t="s">
-        <v>126</v>
+        <v>188</v>
       </c>
       <c r="I46" t="s">
-        <v>154</v>
+        <v>192</v>
       </c>
       <c r="J46">
         <v>5</v>
+      </c>
+      <c r="K46" t="s">
+        <v>178</v>
+      </c>
+      <c r="L46" t="s">
+        <v>165</v>
+      </c>
+      <c r="M46" t="s">
+        <v>165</v>
+      </c>
+      <c r="N46" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="B47" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="C47" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D47" t="s">
-        <v>136</v>
+        <v>22</v>
       </c>
       <c r="E47" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F47" t="s">
         <v>18</v>
       </c>
       <c r="G47" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="H47" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="I47" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="J47">
         <v>5</v>
@@ -2726,166 +2693,74 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="B48" t="s">
-        <v>161</v>
+        <v>108</v>
       </c>
       <c r="C48" t="s">
-        <v>194</v>
+        <v>34</v>
       </c>
       <c r="D48" t="s">
-        <v>195</v>
+        <v>120</v>
       </c>
       <c r="E48" t="s">
-        <v>196</v>
+        <v>149</v>
       </c>
       <c r="F48" t="s">
-        <v>192</v>
+        <v>18</v>
       </c>
       <c r="G48" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="H48" t="s">
-        <v>197</v>
+        <v>110</v>
       </c>
       <c r="I48" t="s">
-        <v>198</v>
+        <v>150</v>
       </c>
       <c r="J48">
         <v>5</v>
       </c>
-      <c r="K48" t="s">
-        <v>187</v>
-      </c>
-      <c r="L48" t="s">
-        <v>174</v>
-      </c>
-      <c r="M48" t="s">
-        <v>174</v>
-      </c>
-      <c r="N48" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B49" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="C49" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D49" t="s">
-        <v>136</v>
+        <v>22</v>
       </c>
       <c r="E49" t="s">
+        <v>39</v>
+      </c>
+      <c r="F49" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" t="s">
+        <v>147</v>
+      </c>
+      <c r="H49" t="s">
+        <v>110</v>
+      </c>
+      <c r="I49" t="s">
         <v>151</v>
       </c>
-      <c r="F49" t="s">
-        <v>18</v>
-      </c>
-      <c r="G49" t="s">
-        <v>156</v>
-      </c>
-      <c r="H49" t="s">
-        <v>126</v>
-      </c>
-      <c r="I49" t="s">
-        <v>157</v>
-      </c>
       <c r="J49">
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A50">
-        <v>361</v>
-      </c>
-      <c r="B50" t="s">
-        <v>124</v>
-      </c>
-      <c r="C50" t="s">
-        <v>51</v>
-      </c>
-      <c r="D50" t="s">
-        <v>158</v>
-      </c>
-      <c r="E50" t="s">
-        <v>159</v>
-      </c>
-      <c r="F50" t="s">
-        <v>18</v>
-      </c>
-      <c r="G50" t="s">
-        <v>156</v>
-      </c>
-      <c r="H50" t="s">
-        <v>126</v>
-      </c>
-      <c r="I50" t="s">
-        <v>160</v>
-      </c>
-      <c r="J50">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A51">
-        <v>362</v>
-      </c>
-      <c r="B51" t="s">
-        <v>161</v>
-      </c>
-      <c r="C51" t="s">
-        <v>200</v>
-      </c>
-      <c r="D51" t="s">
-        <v>195</v>
-      </c>
-      <c r="E51" t="s">
-        <v>196</v>
-      </c>
-      <c r="F51" t="s">
-        <v>192</v>
-      </c>
-      <c r="G51" t="s">
-        <v>156</v>
-      </c>
-      <c r="H51" t="s">
-        <v>197</v>
-      </c>
-      <c r="I51" t="s">
-        <v>201</v>
-      </c>
-      <c r="J51">
-        <v>5</v>
-      </c>
-      <c r="K51" t="s">
-        <v>187</v>
-      </c>
-      <c r="L51" t="s">
-        <v>174</v>
-      </c>
-      <c r="M51" t="s">
-        <v>174</v>
-      </c>
-      <c r="N51" t="s">
-        <v>202</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:N49" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N49">
+      <sortCondition ref="A1:A49"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB0D7E08-75A2-9C4D-9F6A-5C8B1A15FD35}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/resumen_trabajos_1.xlsx
+++ b/resumen_trabajos_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dacm/we/odoo_con_trabajos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA42FCF1-A245-1D4E-BC71-CC4960E3C1BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1CE5DB7-6E26-FA46-9496-21549D460ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36220" yWindow="-4820" windowWidth="33600" windowHeight="19320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4180" yWindow="600" windowWidth="29420" windowHeight="19320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="197">
   <si>
     <t>OT</t>
   </si>
@@ -103,60 +103,7 @@
 Pozo aún se encuentra en periodo de mantenimiento.</t>
   </si>
   <si>
-    <t>Matías Pomar</t>
-  </si>
-  <si>
-    <t>Levantamiento tecnico nuevo punto</t>
-  </si>
-  <si>
-    <t>Farellones</t>
-  </si>
-  <si>
-    <t>[Farellones] Planta de Tratamiento</t>
-  </si>
-  <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t>26/11/2025</t>
-  </si>
-  <si>
-    <t>Felipe Brain</t>
-  </si>
-  <si>
-    <t>Alcance:
-El cliente realizará una intervención en la línea de aducción para habilitar una bifurcación destinada al llenado del tranque. En este punto se instalarán dos válvulas ON/OFF para el control del flujo y un caudalímetro Siemens MAG 5100W para medir el caudal que alimentará el tranque.
-El cliente también informó que construirá una cámara enterrada con tapa, donde quedará instalado el conjunto de válvulas y el caudalímetro. Además, mencionó que puede realizar la instalación mecánica de los equipos, por lo que nosotros debemos considerar la supervisión del montaje y la entrega de planos de canalización. La modificación de la tubería será en HDPE, y es necesario contemplar los anillos del caudalímetro para su correcta instalación. 
-Adicionalmente, se incorporará un switch de comunicaciones que será instalado en la Planta de Tratamiento de Farellones para integrar los equipos LoRa. También se deben considerar los cables y suministros necesarios para el conexionado de los equipos.</t>
-  </si>
-  <si>
     <t>Elías Sanchez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mantenimiento preventivo </t>
-  </si>
-  <si>
-    <t>[Gestión Hídrica El Soldado] Pozo El Melón N° 04 (PEM-04) Nodo A11</t>
-  </si>
-  <si>
-    <t>05/12/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Superintendencia de recursos hidricos </t>
-  </si>
-  <si>
-    <t xml:space="preserve">43 mts esta instalado el sensor hidrostatico 
-Y el pozometro sonó a los 4,10m. 
-Se realiza limpieza al flowcell de la sonda multiparamétrica en el punto. 
-Se anota en Excel interno volumen, Caudal, número de sensor, rango, se revisa programación para corroborar que esta actualizando los datos en el plc. </t>
-  </si>
-  <si>
-    <t>[Gestión Hídrica El Soldado] Pozo El Melón N° 10 (PEM-10) Nodo A16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,16m suena el pozometro
-Se ajusta el sensor hidrostatico a nivel 0 de la superficie, se corrige el total en metros a través de la transformación de presión bar
-Limpieza, reapriete, verificación de programas ecostruxture, que actualice los datos de sonda y de caudal(en funcionamiento) se actualiza  el volumen,limpieza de flowcell. </t>
   </si>
   <si>
     <t xml:space="preserve">Transporte de materiales </t>
@@ -192,6 +139,9 @@
   </si>
   <si>
     <t>Recinto PME-09, P6 Dren Muro Este</t>
+  </si>
+  <si>
+    <t>LT</t>
   </si>
   <si>
     <t xml:space="preserve">Patricio Cortes </t>
@@ -229,6 +179,12 @@
   </si>
   <si>
     <t>[Gestión Hídrica El Soldado] Pozo El Melón N° 06 (PEM-06) Nodo</t>
+  </si>
+  <si>
+    <t>05/12/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Superintendencia de recursos hidricos </t>
   </si>
   <si>
     <t xml:space="preserve">PEM-06
@@ -421,6 +377,9 @@
     <t>Leonardo Gonzalez</t>
   </si>
   <si>
+    <t xml:space="preserve">Mantenimiento preventivo </t>
+  </si>
+  <si>
     <t>[Gestión Hídrica El Soldado] Pozo Los Litres N° 03 (PLL-03) Nodo 168</t>
   </si>
   <si>
@@ -560,9 +519,37 @@
     <t xml:space="preserve">Se realizo inspección visual de cada punto para que no se encontrarán bandalizado o con algún problema. </t>
   </si>
   <si>
+    <t>[Gestión Hídrica El Soldado] Pozo El Melón N° 10 (PEM-10) Nodo A16</t>
+  </si>
+  <si>
     <t>Se da revisión al punto por que ese encontraba caído y dando datos erróneos la sonda. 
 Se deja sonda con agua ya que se encontraba sin agua.
 Válvula estaba abierta. Habían indicios qué el agua había corrido por el piso hacia el exterior.</t>
+  </si>
+  <si>
+    <t>Visita terreno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AAES </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galileo estación reelevadora </t>
+  </si>
+  <si>
+    <t>05/01/2026</t>
+  </si>
+  <si>
+    <t>Se acude al punto a verificar la condición y se anota lo que falta para la habilitación de éste.
+Batería acorde y peinado de cables</t>
+  </si>
+  <si>
+    <t>Gestiones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Se coordina con Joanil Contreras para la entrega de perfil metálico para instalación de lector de velocidad RQ30.
+- Se hace entrega de documentación a Sr. Nicolas solicitado por Rodrigo López.
+- Se espero a don Diego Ramos para la verificación de instalación de los postes en los puntos PEM, pero no fue posible reunirnos, esta coordinado para hoy a las 10:00hrs apox.
+- Se rotula las herramientas acorde al color reactivo de este mes. </t>
   </si>
   <si>
     <t>Ángel Zamora</t>
@@ -713,6 +700,26 @@
   <si>
     <t>PH de entrada en planta Biodiversa zona 1 esta desconectado del equipo, por ende marca dato erroneo.
 En planta Biodiversa vdf ksb pantalla no enciende, voltimetro marca más de 500v puede que el equipo falle lo que provocaría perdida de lecturas modbus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migración Red Lora </t>
+  </si>
+  <si>
+    <t>[Global Tórtolas] Pozo BN7</t>
+  </si>
+  <si>
+    <t>Durante mañana tarde firmas de PT, se retiran equipos de Netaxion.
+Paula Riquelme nos hace entrega de antenas Lora.
+Tiempo restante para migrar BN7 a Lora Wan, se dejan con Paula 21 equipos de estos guardados en su oficina.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uc300 </t>
+  </si>
+  <si>
+    <t>6445F15714530004</t>
+  </si>
+  <si>
+    <t>Punto queda transmitiendo y operativo</t>
   </si>
 </sst>
 </file>
@@ -1125,7 +1132,7 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B2" t="s">
         <v>25</v>
@@ -1140,16 +1147,16 @@
         <v>28</v>
       </c>
       <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
         <v>29</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>30</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>31</v>
-      </c>
-      <c r="I2" t="s">
-        <v>32</v>
       </c>
       <c r="J2">
         <v>5</v>
@@ -1157,31 +1164,31 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
       </c>
       <c r="G3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="I3" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="J3">
         <v>5</v>
@@ -1189,31 +1196,31 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
         <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
       </c>
       <c r="G4" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H4" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="I4" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -1221,31 +1228,31 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
         <v>33</v>
       </c>
-      <c r="C5" t="s">
-        <v>41</v>
-      </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="G5" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="H5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="I5" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="J5">
         <v>5</v>
@@ -1253,63 +1260,75 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>149</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>121</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>150</v>
       </c>
       <c r="F6" t="s">
-        <v>18</v>
+        <v>151</v>
       </c>
       <c r="G6" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H6" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I6" t="s">
-        <v>21</v>
+        <v>152</v>
       </c>
       <c r="J6">
         <v>5</v>
+      </c>
+      <c r="K6" t="s">
+        <v>153</v>
+      </c>
+      <c r="L6" t="s">
+        <v>154</v>
+      </c>
+      <c r="M6" t="s">
+        <v>155</v>
+      </c>
+      <c r="N6" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
       </c>
       <c r="G7" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="H7" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I7" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="J7">
         <v>5</v>
@@ -1317,31 +1336,31 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="G8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" t="s">
         <v>44</v>
-      </c>
-      <c r="H8" t="s">
-        <v>51</v>
-      </c>
-      <c r="I8" t="s">
-        <v>52</v>
       </c>
       <c r="J8">
         <v>5</v>
@@ -1349,78 +1368,90 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B9" t="s">
-        <v>152</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>132</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F9" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="G9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H9" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="I9" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="J9">
         <v>5</v>
       </c>
       <c r="K9" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L9" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="M9" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="N9" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>54</v>
+        <v>157</v>
       </c>
       <c r="F10" t="s">
-        <v>18</v>
+        <v>158</v>
       </c>
       <c r="G10" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="H10" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="I10" t="s">
-        <v>56</v>
+        <v>159</v>
       </c>
       <c r="J10">
         <v>5</v>
+      </c>
+      <c r="K10" t="s">
+        <v>164</v>
+      </c>
+      <c r="L10" t="s">
+        <v>165</v>
+      </c>
+      <c r="M10" t="s">
+        <v>166</v>
+      </c>
+      <c r="N10" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -1431,189 +1462,177 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
         <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>23</v>
+        <v>157</v>
       </c>
       <c r="F11" t="s">
-        <v>18</v>
+        <v>158</v>
       </c>
       <c r="G11" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="H11" t="s">
         <v>20</v>
       </c>
       <c r="I11" t="s">
-        <v>58</v>
+        <v>159</v>
       </c>
       <c r="J11">
         <v>5</v>
+      </c>
+      <c r="K11" t="s">
+        <v>153</v>
+      </c>
+      <c r="L11" t="s">
+        <v>168</v>
+      </c>
+      <c r="M11" t="s">
+        <v>169</v>
+      </c>
+      <c r="N11" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
         <v>22</v>
       </c>
       <c r="E12" t="s">
-        <v>160</v>
+        <v>46</v>
       </c>
       <c r="F12" t="s">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="G12" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="H12" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="I12" t="s">
-        <v>162</v>
+        <v>49</v>
       </c>
       <c r="J12">
         <v>5</v>
-      </c>
-      <c r="K12" t="s">
-        <v>163</v>
-      </c>
-      <c r="L12" t="s">
-        <v>164</v>
-      </c>
-      <c r="M12" t="s">
-        <v>165</v>
-      </c>
-      <c r="N12" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="E13" t="s">
-        <v>160</v>
+        <v>51</v>
       </c>
       <c r="F13" t="s">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="G13" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="H13" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="I13" t="s">
-        <v>162</v>
+        <v>52</v>
       </c>
       <c r="J13">
         <v>5</v>
-      </c>
-      <c r="K13" t="s">
-        <v>167</v>
-      </c>
-      <c r="L13" t="s">
-        <v>168</v>
-      </c>
-      <c r="M13" t="s">
-        <v>169</v>
-      </c>
-      <c r="N13" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>149</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>171</v>
       </c>
       <c r="D14" t="s">
         <v>22</v>
       </c>
       <c r="E14" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="F14" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G14" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="H14" t="s">
-        <v>20</v>
+        <v>173</v>
       </c>
       <c r="I14" t="s">
+        <v>174</v>
+      </c>
+      <c r="J14">
+        <v>5</v>
+      </c>
+      <c r="K14" t="s">
+        <v>175</v>
+      </c>
+      <c r="L14" t="s">
+        <v>176</v>
+      </c>
+      <c r="M14" t="s">
+        <v>177</v>
+      </c>
+      <c r="N14" t="s">
         <v>162</v>
-      </c>
-      <c r="J14">
-        <v>5</v>
-      </c>
-      <c r="K14" t="s">
-        <v>156</v>
-      </c>
-      <c r="L14" t="s">
-        <v>171</v>
-      </c>
-      <c r="M14" t="s">
-        <v>172</v>
-      </c>
-      <c r="N14" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D15" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E15" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
       </c>
       <c r="G15" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H15" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="I15" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="J15">
         <v>5</v>
@@ -1621,31 +1640,31 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" t="s">
+        <v>58</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
         <v>59</v>
       </c>
-      <c r="D16" t="s">
-        <v>62</v>
-      </c>
-      <c r="E16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G16" t="s">
-        <v>36</v>
-      </c>
       <c r="H16" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="I16" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="J16">
         <v>5</v>
@@ -1653,107 +1672,107 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="B17" t="s">
-        <v>152</v>
+        <v>53</v>
       </c>
       <c r="C17" t="s">
-        <v>174</v>
+        <v>61</v>
       </c>
       <c r="D17" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E17" t="s">
-        <v>175</v>
+        <v>40</v>
       </c>
       <c r="F17" t="s">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="G17" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="H17" t="s">
-        <v>176</v>
+        <v>30</v>
       </c>
       <c r="I17" t="s">
-        <v>177</v>
+        <v>63</v>
       </c>
       <c r="J17">
         <v>5</v>
-      </c>
-      <c r="K17" t="s">
-        <v>178</v>
-      </c>
-      <c r="L17" t="s">
-        <v>179</v>
-      </c>
-      <c r="M17" t="s">
-        <v>180</v>
-      </c>
-      <c r="N17" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>149</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>178</v>
       </c>
       <c r="D18" t="s">
-        <v>42</v>
+        <v>121</v>
       </c>
       <c r="E18" t="s">
-        <v>54</v>
+        <v>179</v>
       </c>
       <c r="F18" t="s">
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="G18" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H18" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="I18" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="J18">
         <v>5</v>
+      </c>
+      <c r="K18" t="s">
+        <v>175</v>
+      </c>
+      <c r="L18" t="s">
+        <v>162</v>
+      </c>
+      <c r="M18" t="s">
+        <v>162</v>
+      </c>
+      <c r="N18" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D19" t="s">
         <v>22</v>
       </c>
       <c r="E19" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F19" t="s">
         <v>18</v>
       </c>
       <c r="G19" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H19" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="I19" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="J19">
         <v>5</v>
@@ -1761,31 +1780,31 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B20" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D20" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="E20" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="F20" t="s">
         <v>18</v>
       </c>
       <c r="G20" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="H20" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I20" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="J20">
         <v>5</v>
@@ -1793,75 +1812,63 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B21" t="s">
-        <v>152</v>
+        <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>181</v>
+        <v>67</v>
       </c>
       <c r="D21" t="s">
-        <v>132</v>
+        <v>22</v>
       </c>
       <c r="E21" t="s">
-        <v>182</v>
+        <v>71</v>
       </c>
       <c r="F21" t="s">
-        <v>183</v>
+        <v>18</v>
       </c>
       <c r="G21" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="H21" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I21" t="s">
-        <v>184</v>
+        <v>72</v>
       </c>
       <c r="J21">
         <v>5</v>
-      </c>
-      <c r="K21" t="s">
-        <v>178</v>
-      </c>
-      <c r="L21" t="s">
-        <v>165</v>
-      </c>
-      <c r="M21" t="s">
-        <v>165</v>
-      </c>
-      <c r="N21" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D22" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E22" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="F22" t="s">
         <v>18</v>
       </c>
       <c r="G22" t="s">
+        <v>69</v>
+      </c>
+      <c r="H22" t="s">
+        <v>55</v>
+      </c>
+      <c r="I22" t="s">
         <v>74</v>
-      </c>
-      <c r="H22" t="s">
-        <v>37</v>
-      </c>
-      <c r="I22" t="s">
-        <v>78</v>
       </c>
       <c r="J22">
         <v>5</v>
@@ -1869,31 +1876,31 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D23" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E23" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="F23" t="s">
         <v>18</v>
       </c>
       <c r="G23" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H23" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="I23" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J23">
         <v>5</v>
@@ -1901,31 +1908,31 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D24" t="s">
         <v>22</v>
       </c>
       <c r="E24" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="F24" t="s">
         <v>18</v>
       </c>
       <c r="G24" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H24" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="I24" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="J24">
         <v>5</v>
@@ -1933,31 +1940,31 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B25" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="C25" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D25" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="E25" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="F25" t="s">
         <v>18</v>
       </c>
       <c r="G25" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H25" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="I25" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="J25">
         <v>5</v>
@@ -1965,31 +1972,31 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B26" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="C26" t="s">
+        <v>84</v>
+      </c>
+      <c r="D26" t="s">
+        <v>85</v>
+      </c>
+      <c r="E26" t="s">
+        <v>86</v>
+      </c>
+      <c r="F26" t="s">
         <v>87</v>
-      </c>
-      <c r="D26" t="s">
-        <v>42</v>
-      </c>
-      <c r="E26" t="s">
-        <v>54</v>
-      </c>
-      <c r="F26" t="s">
-        <v>18</v>
       </c>
       <c r="G26" t="s">
         <v>88</v>
       </c>
       <c r="H26" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="I26" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J26">
         <v>5</v>
@@ -1997,31 +2004,31 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D27" t="s">
-        <v>22</v>
+        <v>92</v>
       </c>
       <c r="E27" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="F27" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="G27" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H27" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="I27" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J27">
         <v>5</v>
@@ -2029,16 +2036,16 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B28" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C28" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D28" t="s">
-        <v>22</v>
+        <v>92</v>
       </c>
       <c r="E28" t="s">
         <v>93</v>
@@ -2047,13 +2054,13 @@
         <v>18</v>
       </c>
       <c r="G28" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H28" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="I28" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J28">
         <v>5</v>
@@ -2061,31 +2068,31 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D29" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="E29" t="s">
         <v>98</v>
       </c>
       <c r="F29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" t="s">
+        <v>88</v>
+      </c>
+      <c r="H29" t="s">
         <v>99</v>
       </c>
-      <c r="G29" t="s">
+      <c r="I29" t="s">
         <v>100</v>
-      </c>
-      <c r="H29" t="s">
-        <v>101</v>
-      </c>
-      <c r="I29" t="s">
-        <v>102</v>
       </c>
       <c r="J29">
         <v>5</v>
@@ -2093,31 +2100,31 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="C30" t="s">
+        <v>101</v>
+      </c>
+      <c r="D30" t="s">
+        <v>102</v>
+      </c>
+      <c r="E30" t="s">
         <v>103</v>
       </c>
-      <c r="D30" t="s">
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" t="s">
+        <v>94</v>
+      </c>
+      <c r="H30" t="s">
         <v>104</v>
       </c>
-      <c r="E30" t="s">
+      <c r="I30" t="s">
         <v>105</v>
-      </c>
-      <c r="F30" t="s">
-        <v>29</v>
-      </c>
-      <c r="G30" t="s">
-        <v>106</v>
-      </c>
-      <c r="H30" t="s">
-        <v>45</v>
-      </c>
-      <c r="I30" t="s">
-        <v>107</v>
       </c>
       <c r="J30">
         <v>5</v>
@@ -2125,31 +2132,31 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C31" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D31" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="E31" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F31" t="s">
         <v>18</v>
       </c>
       <c r="G31" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H31" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I31" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J31">
         <v>5</v>
@@ -2157,28 +2164,28 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B32" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C32" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="D32" t="s">
-        <v>22</v>
+        <v>109</v>
       </c>
       <c r="E32" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F32" t="s">
         <v>18</v>
       </c>
       <c r="G32" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H32" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="I32" t="s">
         <v>111</v>
@@ -2189,31 +2196,31 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B33" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C33" t="s">
+        <v>97</v>
+      </c>
+      <c r="D33" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33" t="s">
         <v>112</v>
       </c>
-      <c r="D33" t="s">
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" t="s">
+        <v>94</v>
+      </c>
+      <c r="H33" t="s">
+        <v>99</v>
+      </c>
+      <c r="I33" t="s">
         <v>113</v>
-      </c>
-      <c r="E33" t="s">
-        <v>114</v>
-      </c>
-      <c r="F33" t="s">
-        <v>18</v>
-      </c>
-      <c r="G33" t="s">
-        <v>106</v>
-      </c>
-      <c r="H33" t="s">
-        <v>115</v>
-      </c>
-      <c r="I33" t="s">
-        <v>116</v>
       </c>
       <c r="J33">
         <v>5</v>
@@ -2221,31 +2228,31 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B34" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="C34" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="D34" t="s">
-        <v>105</v>
+        <v>22</v>
       </c>
       <c r="E34" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F34" t="s">
         <v>18</v>
       </c>
       <c r="G34" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="H34" t="s">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="I34" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="J34">
         <v>5</v>
@@ -2253,31 +2260,31 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B35" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C35" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="D35" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="E35" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F35" t="s">
         <v>18</v>
       </c>
       <c r="G35" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="H35" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="I35" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J35">
         <v>5</v>
@@ -2285,28 +2292,28 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="B36" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="C36" t="s">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="D36" t="s">
-        <v>22</v>
+        <v>121</v>
       </c>
       <c r="E36" t="s">
+        <v>122</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" t="s">
         <v>123</v>
       </c>
-      <c r="F36" t="s">
-        <v>18</v>
-      </c>
-      <c r="G36" t="s">
-        <v>106</v>
-      </c>
       <c r="H36" t="s">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="I36" t="s">
         <v>124</v>
@@ -2317,16 +2324,16 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B37" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C37" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="D37" t="s">
-        <v>22</v>
+        <v>109</v>
       </c>
       <c r="E37" t="s">
         <v>125</v>
@@ -2338,7 +2345,7 @@
         <v>126</v>
       </c>
       <c r="H37" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="I37" t="s">
         <v>127</v>
@@ -2349,31 +2356,31 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B38" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C38" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="D38" t="s">
-        <v>120</v>
+        <v>22</v>
       </c>
       <c r="E38" t="s">
+        <v>114</v>
+      </c>
+      <c r="F38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" t="s">
+        <v>126</v>
+      </c>
+      <c r="H38" t="s">
+        <v>99</v>
+      </c>
+      <c r="I38" t="s">
         <v>128</v>
-      </c>
-      <c r="F38" t="s">
-        <v>18</v>
-      </c>
-      <c r="G38" t="s">
-        <v>129</v>
-      </c>
-      <c r="H38" t="s">
-        <v>110</v>
-      </c>
-      <c r="I38" t="s">
-        <v>130</v>
       </c>
       <c r="J38">
         <v>5</v>
@@ -2381,31 +2388,31 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B39" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="C39" t="s">
-        <v>131</v>
+        <v>97</v>
       </c>
       <c r="D39" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="E39" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F39" t="s">
         <v>18</v>
       </c>
       <c r="G39" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H39" t="s">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="I39" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="J39">
         <v>5</v>
@@ -2413,48 +2420,60 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B40" t="s">
-        <v>108</v>
+        <v>149</v>
       </c>
       <c r="C40" t="s">
-        <v>34</v>
+        <v>182</v>
       </c>
       <c r="D40" t="s">
-        <v>120</v>
+        <v>183</v>
       </c>
       <c r="E40" t="s">
-        <v>136</v>
+        <v>184</v>
       </c>
       <c r="F40" t="s">
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="G40" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="H40" t="s">
-        <v>110</v>
+        <v>185</v>
       </c>
       <c r="I40" t="s">
-        <v>138</v>
+        <v>186</v>
       </c>
       <c r="J40">
         <v>5</v>
+      </c>
+      <c r="K40" t="s">
+        <v>175</v>
+      </c>
+      <c r="L40" t="s">
+        <v>162</v>
+      </c>
+      <c r="M40" t="s">
+        <v>162</v>
+      </c>
+      <c r="N40" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B41" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C41" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="D41" t="s">
-        <v>22</v>
+        <v>109</v>
       </c>
       <c r="E41" t="s">
         <v>125</v>
@@ -2463,13 +2482,13 @@
         <v>18</v>
       </c>
       <c r="G41" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="H41" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="I41" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="J41">
         <v>5</v>
@@ -2477,31 +2496,31 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B42" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C42" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="D42" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="E42" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F42" t="s">
         <v>18</v>
       </c>
       <c r="G42" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="H42" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="I42" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="J42">
         <v>5</v>
@@ -2509,28 +2528,28 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B43" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C43" t="s">
+        <v>188</v>
+      </c>
+      <c r="D43" t="s">
+        <v>183</v>
+      </c>
+      <c r="E43" t="s">
+        <v>184</v>
+      </c>
+      <c r="F43" t="s">
+        <v>180</v>
+      </c>
+      <c r="G43" t="s">
+        <v>130</v>
+      </c>
+      <c r="H43" t="s">
         <v>185</v>
-      </c>
-      <c r="D43" t="s">
-        <v>186</v>
-      </c>
-      <c r="E43" t="s">
-        <v>187</v>
-      </c>
-      <c r="F43" t="s">
-        <v>183</v>
-      </c>
-      <c r="G43" t="s">
-        <v>141</v>
-      </c>
-      <c r="H43" t="s">
-        <v>188</v>
       </c>
       <c r="I43" t="s">
         <v>189</v>
@@ -2539,13 +2558,13 @@
         <v>5</v>
       </c>
       <c r="K43" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="L43" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="M43" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="N43" t="s">
         <v>190</v>
@@ -2553,31 +2572,31 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B44" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C44" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="D44" t="s">
-        <v>120</v>
+        <v>22</v>
       </c>
       <c r="E44" t="s">
+        <v>135</v>
+      </c>
+      <c r="F44" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" t="s">
         <v>136</v>
       </c>
-      <c r="F44" t="s">
-        <v>18</v>
-      </c>
-      <c r="G44" t="s">
-        <v>141</v>
-      </c>
       <c r="H44" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="I44" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="J44">
         <v>5</v>
@@ -2585,31 +2604,31 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B45" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C45" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="D45" t="s">
-        <v>143</v>
+        <v>109</v>
       </c>
       <c r="E45" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F45" t="s">
         <v>18</v>
       </c>
       <c r="G45" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="H45" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="I45" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="J45">
         <v>5</v>
@@ -2617,107 +2636,107 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B46" t="s">
-        <v>152</v>
+        <v>96</v>
       </c>
       <c r="C46" t="s">
-        <v>191</v>
+        <v>97</v>
       </c>
       <c r="D46" t="s">
-        <v>186</v>
+        <v>22</v>
       </c>
       <c r="E46" t="s">
-        <v>187</v>
+        <v>140</v>
       </c>
       <c r="F46" t="s">
-        <v>183</v>
+        <v>18</v>
       </c>
       <c r="G46" t="s">
+        <v>136</v>
+      </c>
+      <c r="H46" t="s">
+        <v>99</v>
+      </c>
+      <c r="I46" t="s">
         <v>141</v>
       </c>
-      <c r="H46" t="s">
-        <v>188</v>
-      </c>
-      <c r="I46" t="s">
-        <v>192</v>
-      </c>
       <c r="J46">
         <v>5</v>
-      </c>
-      <c r="K46" t="s">
-        <v>178</v>
-      </c>
-      <c r="L46" t="s">
-        <v>165</v>
-      </c>
-      <c r="M46" t="s">
-        <v>165</v>
-      </c>
-      <c r="N46" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B47" t="s">
-        <v>108</v>
+        <v>149</v>
       </c>
       <c r="C47" t="s">
-        <v>34</v>
+        <v>191</v>
       </c>
       <c r="D47" t="s">
-        <v>22</v>
+        <v>121</v>
       </c>
       <c r="E47" t="s">
-        <v>146</v>
+        <v>192</v>
       </c>
       <c r="F47" t="s">
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="G47" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H47" t="s">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="I47" t="s">
-        <v>148</v>
+        <v>193</v>
       </c>
       <c r="J47">
         <v>5</v>
+      </c>
+      <c r="K47" t="s">
+        <v>175</v>
+      </c>
+      <c r="L47" t="s">
+        <v>194</v>
+      </c>
+      <c r="M47" t="s">
+        <v>195</v>
+      </c>
+      <c r="N47" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B48" t="s">
-        <v>108</v>
+        <v>25</v>
       </c>
       <c r="C48" t="s">
-        <v>34</v>
+        <v>142</v>
       </c>
       <c r="D48" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="E48" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F48" t="s">
         <v>18</v>
       </c>
       <c r="G48" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H48" t="s">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="I48" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="J48">
         <v>5</v>
@@ -2725,31 +2744,31 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B49" t="s">
-        <v>108</v>
+        <v>25</v>
       </c>
       <c r="C49" t="s">
-        <v>34</v>
+        <v>142</v>
       </c>
       <c r="D49" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="E49" t="s">
-        <v>39</v>
+        <v>147</v>
       </c>
       <c r="F49" t="s">
         <v>18</v>
       </c>
       <c r="G49" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H49" t="s">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="I49" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="J49">
         <v>5</v>

--- a/resumen_trabajos_1.xlsx
+++ b/resumen_trabajos_1.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dacm/we/odoo_con_trabajos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1CE5DB7-6E26-FA46-9496-21549D460ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B3DD152-8EF6-C24E-9586-07A1D71B7A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4180" yWindow="600" windowWidth="29420" windowHeight="19320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2840" yWindow="1460" windowWidth="29420" windowHeight="19320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$52</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="211">
   <si>
     <t>OT</t>
   </si>
@@ -103,60 +103,46 @@
 Pozo aún se encuentra en periodo de mantenimiento.</t>
   </si>
   <si>
+    <t>Juan José López</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validación de variables </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calidad de aguas </t>
+  </si>
+  <si>
+    <t>Recinto PME-09, P6 Dren Muro Este</t>
+  </si>
+  <si>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>10/12/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patricio Cortes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se realiza revicion de variables en los recintos </t>
+  </si>
+  <si>
     <t>Elías Sanchez</t>
   </si>
   <si>
-    <t xml:space="preserve">Transporte de materiales </t>
+    <t xml:space="preserve">Traslado de materiales </t>
   </si>
   <si>
     <t>Los Bronces - Riecillos</t>
   </si>
   <si>
-    <t>Patio de tuberias</t>
-  </si>
-  <si>
-    <t>10/12/2025</t>
+    <t>[Los Bronces - Riecillos] R2700 Gateway</t>
+  </si>
+  <si>
+    <t>11/12/2025</t>
   </si>
   <si>
     <t xml:space="preserve">Paula Riquelme </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se realiza escolta a camión y acopio de materiales ingresados a Patio de tuberías los cuales corresponden a:
-- 2 baterías de 200AH
-- 3 paneles solares de 550W
-- 1 inversor fotovoltaico. 
-Se gestionan permisos para que empresa san Isidro pueda apoyarnos en realizar el montaje de andamios, así mismo el transporte de materiales al punto y así posteriormente montar la estructura de los paneles. 
-</t>
-  </si>
-  <si>
-    <t>Juan José López</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validación de variables </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calidad de aguas </t>
-  </si>
-  <si>
-    <t>Recinto PME-09, P6 Dren Muro Este</t>
-  </si>
-  <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patricio Cortes </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se realiza revicion de variables en los recintos </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Traslado de materiales </t>
-  </si>
-  <si>
-    <t>[Los Bronces - Riecillos] R2700 Gateway</t>
-  </si>
-  <si>
-    <t>11/12/2025</t>
   </si>
   <si>
     <t xml:space="preserve">Se realiza apoyo a camión pluma de GeoBarra para traslado de andamio hasta sala de bombas 2700. Se hace entrega de estructura andamio para su montaje por parte de empresa San Isidro.
@@ -552,6 +538,17 @@
 - Se rotula las herramientas acorde al color reactivo de este mes. </t>
   </si>
   <si>
+    <t>Configuración telemetria pozo BN12</t>
+  </si>
+  <si>
+    <t>06/01/2026</t>
+  </si>
+  <si>
+    <t>Se intstala sensor de nivel en pozo y se configura el equipo junto con el flujometro a traves de lecturas modbus, se comprueban valores en PLC.
+Por otro lado se configura la comunicación del punto a la telemetria WeTechs para la visualizacion de datos.
+Adicionalmente se instalan equipos de comunicación para la lectura de datos a través de red LORA.</t>
+  </si>
+  <si>
     <t>Ángel Zamora</t>
   </si>
   <si>
@@ -720,6 +717,48 @@
   </si>
   <si>
     <t>Punto queda transmitiendo y operativo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migración a Red Lora Wan LT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matias Signorio - Paula Riquelme </t>
+  </si>
+  <si>
+    <t>Se instalan y configuración dispositivo red Lora Wan, se validan datos terreno plataforma ok + antena ok.</t>
+  </si>
+  <si>
+    <t>Uc300-915M</t>
+  </si>
+  <si>
+    <t>6445F17824030004</t>
+  </si>
+  <si>
+    <t>Punto ok.</t>
+  </si>
+  <si>
+    <t>[Global Tórtolas] Pozo BN1</t>
+  </si>
+  <si>
+    <t>Se instalan y configuración dispositivo red Lora Wan, se validan datos terreno plataforma ok. + antena</t>
+  </si>
+  <si>
+    <t>6445F15707350005</t>
+  </si>
+  <si>
+    <t>Punto transmisión de datos ok.</t>
+  </si>
+  <si>
+    <t>Se instalan y configuración dispositivo red Lora Wan, se validan datos terreno plataforma ok. + antena ok.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uc300-915M </t>
+  </si>
+  <si>
+    <t>6445F15534110005</t>
+  </si>
+  <si>
+    <t>Punto con transmisión de datos ok.</t>
   </si>
 </sst>
 </file>
@@ -1083,7 +1122,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N49"/>
+  <dimension ref="A1:N52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
@@ -1132,31 +1171,31 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
       </c>
       <c r="G2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J2">
         <v>5</v>
@@ -1173,10 +1212,10 @@
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -1188,7 +1227,7 @@
         <v>20</v>
       </c>
       <c r="I3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J3">
         <v>5</v>
@@ -1196,31 +1235,31 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F4" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="G4" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="I4" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -1228,107 +1267,107 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>149</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>118</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>150</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
+        <v>151</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I5" t="s">
-        <v>38</v>
+        <v>152</v>
       </c>
       <c r="J5">
         <v>5</v>
+      </c>
+      <c r="K5" t="s">
+        <v>153</v>
+      </c>
+      <c r="L5" t="s">
+        <v>154</v>
+      </c>
+      <c r="M5" t="s">
+        <v>155</v>
+      </c>
+      <c r="N5" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B6" t="s">
-        <v>149</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>121</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>150</v>
+        <v>36</v>
       </c>
       <c r="F6" t="s">
-        <v>151</v>
+        <v>18</v>
       </c>
       <c r="G6" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="H6" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I6" t="s">
-        <v>152</v>
+        <v>39</v>
       </c>
       <c r="J6">
         <v>5</v>
-      </c>
-      <c r="K6" t="s">
-        <v>153</v>
-      </c>
-      <c r="L6" t="s">
-        <v>154</v>
-      </c>
-      <c r="M6" t="s">
-        <v>155</v>
-      </c>
-      <c r="N6" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
       </c>
       <c r="G7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" t="s">
         <v>41</v>
-      </c>
-      <c r="H7" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" t="s">
-        <v>42</v>
       </c>
       <c r="J7">
         <v>5</v>
@@ -1342,28 +1381,40 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
         <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>157</v>
       </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>158</v>
       </c>
       <c r="G8" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H8" t="s">
         <v>20</v>
       </c>
       <c r="I8" t="s">
-        <v>44</v>
+        <v>159</v>
       </c>
       <c r="J8">
         <v>5</v>
+      </c>
+      <c r="K8" t="s">
+        <v>160</v>
+      </c>
+      <c r="L8" t="s">
+        <v>161</v>
+      </c>
+      <c r="M8" t="s">
+        <v>162</v>
+      </c>
+      <c r="N8" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -1374,7 +1425,7 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
         <v>22</v>
@@ -1386,7 +1437,7 @@
         <v>158</v>
       </c>
       <c r="G9" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H9" t="s">
         <v>20</v>
@@ -1398,16 +1449,16 @@
         <v>5</v>
       </c>
       <c r="K9" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="L9" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="M9" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="N9" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -1418,7 +1469,7 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
         <v>22</v>
@@ -1430,7 +1481,7 @@
         <v>158</v>
       </c>
       <c r="G10" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H10" t="s">
         <v>20</v>
@@ -1442,60 +1493,48 @@
         <v>5</v>
       </c>
       <c r="K10" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="L10" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="M10" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="N10" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
         <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>157</v>
+        <v>43</v>
       </c>
       <c r="F11" t="s">
-        <v>158</v>
+        <v>18</v>
       </c>
       <c r="G11" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H11" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="I11" t="s">
-        <v>159</v>
+        <v>46</v>
       </c>
       <c r="J11">
         <v>5</v>
-      </c>
-      <c r="K11" t="s">
-        <v>153</v>
-      </c>
-      <c r="L11" t="s">
-        <v>168</v>
-      </c>
-      <c r="M11" t="s">
-        <v>169</v>
-      </c>
-      <c r="N11" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -1503,25 +1542,25 @@
         <v>327</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
+        <v>44</v>
+      </c>
+      <c r="H12" t="s">
         <v>45</v>
-      </c>
-      <c r="D12" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12" t="s">
-        <v>18</v>
-      </c>
-      <c r="G12" t="s">
-        <v>47</v>
-      </c>
-      <c r="H12" t="s">
-        <v>48</v>
       </c>
       <c r="I12" t="s">
         <v>49</v>
@@ -1532,107 +1571,107 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>149</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>171</v>
       </c>
       <c r="D13" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="E13" t="s">
-        <v>51</v>
+        <v>172</v>
       </c>
       <c r="F13" t="s">
-        <v>18</v>
+        <v>158</v>
       </c>
       <c r="G13" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="H13" t="s">
-        <v>48</v>
+        <v>173</v>
       </c>
       <c r="I13" t="s">
-        <v>52</v>
+        <v>174</v>
       </c>
       <c r="J13">
         <v>5</v>
+      </c>
+      <c r="K13" t="s">
+        <v>175</v>
+      </c>
+      <c r="L13" t="s">
+        <v>176</v>
+      </c>
+      <c r="M13" t="s">
+        <v>177</v>
+      </c>
+      <c r="N13" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B14" t="s">
-        <v>149</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>171</v>
+        <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E14" t="s">
-        <v>172</v>
+        <v>36</v>
       </c>
       <c r="F14" t="s">
-        <v>158</v>
+        <v>18</v>
       </c>
       <c r="G14" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H14" t="s">
-        <v>173</v>
+        <v>52</v>
       </c>
       <c r="I14" t="s">
-        <v>174</v>
+        <v>53</v>
       </c>
       <c r="J14">
         <v>5</v>
-      </c>
-      <c r="K14" t="s">
-        <v>175</v>
-      </c>
-      <c r="L14" t="s">
-        <v>176</v>
-      </c>
-      <c r="M14" t="s">
-        <v>177</v>
-      </c>
-      <c r="N14" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B15" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
         <v>54</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
       </c>
       <c r="G15" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="H15" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="I15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J15">
         <v>5</v>
@@ -1640,19 +1679,19 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E16" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
@@ -1661,7 +1700,7 @@
         <v>59</v>
       </c>
       <c r="H16" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="I16" t="s">
         <v>60</v>
@@ -1672,86 +1711,86 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B17" t="s">
-        <v>53</v>
+        <v>149</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>178</v>
       </c>
       <c r="D17" t="s">
-        <v>27</v>
+        <v>118</v>
       </c>
       <c r="E17" t="s">
-        <v>40</v>
+        <v>179</v>
       </c>
       <c r="F17" t="s">
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="G17" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H17" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I17" t="s">
-        <v>63</v>
+        <v>181</v>
       </c>
       <c r="J17">
         <v>5</v>
+      </c>
+      <c r="K17" t="s">
+        <v>175</v>
+      </c>
+      <c r="L17" t="s">
+        <v>162</v>
+      </c>
+      <c r="M17" t="s">
+        <v>162</v>
+      </c>
+      <c r="N17" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B18" t="s">
-        <v>149</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>178</v>
+        <v>61</v>
       </c>
       <c r="D18" t="s">
-        <v>121</v>
+        <v>22</v>
       </c>
       <c r="E18" t="s">
-        <v>179</v>
+        <v>62</v>
       </c>
       <c r="F18" t="s">
-        <v>180</v>
+        <v>18</v>
       </c>
       <c r="G18" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H18" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I18" t="s">
-        <v>181</v>
+        <v>63</v>
       </c>
       <c r="J18">
         <v>5</v>
-      </c>
-      <c r="K18" t="s">
-        <v>175</v>
-      </c>
-      <c r="L18" t="s">
-        <v>162</v>
-      </c>
-      <c r="M18" t="s">
-        <v>162</v>
-      </c>
-      <c r="N18" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C19" t="s">
         <v>64</v>
@@ -1766,13 +1805,13 @@
         <v>18</v>
       </c>
       <c r="G19" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H19" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J19">
         <v>5</v>
@@ -1783,10 +1822,10 @@
         <v>339</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D20" t="s">
         <v>22</v>
@@ -1798,13 +1837,13 @@
         <v>18</v>
       </c>
       <c r="G20" t="s">
+        <v>66</v>
+      </c>
+      <c r="H20" t="s">
+        <v>45</v>
+      </c>
+      <c r="I20" t="s">
         <v>69</v>
-      </c>
-      <c r="H20" t="s">
-        <v>48</v>
-      </c>
-      <c r="I20" t="s">
-        <v>70</v>
       </c>
       <c r="J20">
         <v>5</v>
@@ -1812,31 +1851,31 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B21" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D21" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E21" t="s">
+        <v>36</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H21" t="s">
+        <v>52</v>
+      </c>
+      <c r="I21" t="s">
         <v>71</v>
-      </c>
-      <c r="F21" t="s">
-        <v>18</v>
-      </c>
-      <c r="G21" t="s">
-        <v>69</v>
-      </c>
-      <c r="H21" t="s">
-        <v>48</v>
-      </c>
-      <c r="I21" t="s">
-        <v>72</v>
       </c>
       <c r="J21">
         <v>5</v>
@@ -1844,28 +1883,28 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B22" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
+        <v>72</v>
+      </c>
+      <c r="D22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" t="s">
         <v>73</v>
       </c>
-      <c r="D22" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22" t="s">
-        <v>40</v>
-      </c>
-      <c r="F22" t="s">
-        <v>18</v>
-      </c>
-      <c r="G22" t="s">
-        <v>69</v>
-      </c>
       <c r="H22" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="I22" t="s">
         <v>74</v>
@@ -1876,19 +1915,19 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B23" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="C23" t="s">
         <v>75</v>
       </c>
       <c r="D23" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E23" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="F23" t="s">
         <v>18</v>
@@ -1897,7 +1936,7 @@
         <v>76</v>
       </c>
       <c r="H23" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I23" t="s">
         <v>77</v>
@@ -1911,28 +1950,28 @@
         <v>342</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D24" t="s">
         <v>22</v>
       </c>
       <c r="E24" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="F24" t="s">
         <v>18</v>
       </c>
       <c r="G24" t="s">
+        <v>76</v>
+      </c>
+      <c r="H24" t="s">
+        <v>45</v>
+      </c>
+      <c r="I24" t="s">
         <v>79</v>
-      </c>
-      <c r="H24" t="s">
-        <v>48</v>
-      </c>
-      <c r="I24" t="s">
-        <v>80</v>
       </c>
       <c r="J24">
         <v>5</v>
@@ -1940,31 +1979,31 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D25" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="E25" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F25" t="s">
-        <v>18</v>
+        <v>84</v>
       </c>
       <c r="G25" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H25" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="I25" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="J25">
         <v>5</v>
@@ -1972,31 +2011,31 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="C26" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E26" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F26" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="G26" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H26" t="s">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="I26" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J26">
         <v>5</v>
@@ -2007,28 +2046,28 @@
         <v>345</v>
       </c>
       <c r="B27" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C27" t="s">
+        <v>88</v>
+      </c>
+      <c r="D27" t="s">
+        <v>89</v>
+      </c>
+      <c r="E27" t="s">
+        <v>90</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" t="s">
         <v>91</v>
       </c>
-      <c r="D27" t="s">
+      <c r="H27" t="s">
+        <v>38</v>
+      </c>
+      <c r="I27" t="s">
         <v>92</v>
-      </c>
-      <c r="E27" t="s">
-        <v>93</v>
-      </c>
-      <c r="F27" t="s">
-        <v>36</v>
-      </c>
-      <c r="G27" t="s">
-        <v>94</v>
-      </c>
-      <c r="H27" t="s">
-        <v>30</v>
-      </c>
-      <c r="I27" t="s">
-        <v>95</v>
       </c>
       <c r="J27">
         <v>5</v>
@@ -2036,31 +2075,31 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B28" t="s">
-        <v>25</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D28" t="s">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="E28" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F28" t="s">
         <v>18</v>
       </c>
       <c r="G28" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="H28" t="s">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="I28" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J28">
         <v>5</v>
@@ -2068,31 +2107,31 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="C29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D29" t="s">
-        <v>22</v>
+        <v>99</v>
       </c>
       <c r="E29" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F29" t="s">
         <v>18</v>
       </c>
       <c r="G29" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H29" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I29" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J29">
         <v>5</v>
@@ -2100,28 +2139,28 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B30" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D30" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="E30" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F30" t="s">
         <v>18</v>
       </c>
       <c r="G30" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H30" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="I30" t="s">
         <v>105</v>
@@ -2132,16 +2171,16 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B31" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="C31" t="s">
+        <v>94</v>
+      </c>
+      <c r="D31" t="s">
         <v>106</v>
-      </c>
-      <c r="D31" t="s">
-        <v>93</v>
       </c>
       <c r="E31" t="s">
         <v>107</v>
@@ -2150,10 +2189,10 @@
         <v>18</v>
       </c>
       <c r="G31" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H31" t="s">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="I31" t="s">
         <v>108</v>
@@ -2167,28 +2206,28 @@
         <v>351</v>
       </c>
       <c r="B32" t="s">
+        <v>93</v>
+      </c>
+      <c r="C32" t="s">
+        <v>94</v>
+      </c>
+      <c r="D32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E32" t="s">
+        <v>109</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" t="s">
+        <v>91</v>
+      </c>
+      <c r="H32" t="s">
         <v>96</v>
       </c>
-      <c r="C32" t="s">
-        <v>97</v>
-      </c>
-      <c r="D32" t="s">
-        <v>109</v>
-      </c>
-      <c r="E32" t="s">
+      <c r="I32" t="s">
         <v>110</v>
-      </c>
-      <c r="F32" t="s">
-        <v>18</v>
-      </c>
-      <c r="G32" t="s">
-        <v>94</v>
-      </c>
-      <c r="H32" t="s">
-        <v>99</v>
-      </c>
-      <c r="I32" t="s">
-        <v>111</v>
       </c>
       <c r="J32">
         <v>5</v>
@@ -2196,28 +2235,28 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D33" t="s">
         <v>22</v>
       </c>
       <c r="E33" t="s">
+        <v>111</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" t="s">
         <v>112</v>
       </c>
-      <c r="F33" t="s">
-        <v>18</v>
-      </c>
-      <c r="G33" t="s">
-        <v>94</v>
-      </c>
       <c r="H33" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I33" t="s">
         <v>113</v>
@@ -2228,16 +2267,16 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B34" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C34" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D34" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="E34" t="s">
         <v>114</v>
@@ -2249,7 +2288,7 @@
         <v>115</v>
       </c>
       <c r="H34" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I34" t="s">
         <v>116</v>
@@ -2260,31 +2299,31 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B35" t="s">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="C35" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="D35" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="E35" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F35" t="s">
         <v>18</v>
       </c>
       <c r="G35" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H35" t="s">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="I35" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J35">
         <v>5</v>
@@ -2292,16 +2331,16 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B36" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="C36" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="D36" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="E36" t="s">
         <v>122</v>
@@ -2313,7 +2352,7 @@
         <v>123</v>
       </c>
       <c r="H36" t="s">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="I36" t="s">
         <v>124</v>
@@ -2327,28 +2366,28 @@
         <v>357</v>
       </c>
       <c r="B37" t="s">
+        <v>93</v>
+      </c>
+      <c r="C37" t="s">
+        <v>94</v>
+      </c>
+      <c r="D37" t="s">
+        <v>22</v>
+      </c>
+      <c r="E37" t="s">
+        <v>111</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" t="s">
+        <v>123</v>
+      </c>
+      <c r="H37" t="s">
         <v>96</v>
       </c>
-      <c r="C37" t="s">
-        <v>97</v>
-      </c>
-      <c r="D37" t="s">
-        <v>109</v>
-      </c>
-      <c r="E37" t="s">
+      <c r="I37" t="s">
         <v>125</v>
-      </c>
-      <c r="F37" t="s">
-        <v>18</v>
-      </c>
-      <c r="G37" t="s">
-        <v>126</v>
-      </c>
-      <c r="H37" t="s">
-        <v>99</v>
-      </c>
-      <c r="I37" t="s">
-        <v>127</v>
       </c>
       <c r="J37">
         <v>5</v>
@@ -2359,28 +2398,28 @@
         <v>357</v>
       </c>
       <c r="B38" t="s">
+        <v>93</v>
+      </c>
+      <c r="C38" t="s">
+        <v>94</v>
+      </c>
+      <c r="D38" t="s">
+        <v>106</v>
+      </c>
+      <c r="E38" t="s">
+        <v>122</v>
+      </c>
+      <c r="F38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" t="s">
+        <v>123</v>
+      </c>
+      <c r="H38" t="s">
         <v>96</v>
       </c>
-      <c r="C38" t="s">
-        <v>97</v>
-      </c>
-      <c r="D38" t="s">
-        <v>22</v>
-      </c>
-      <c r="E38" t="s">
-        <v>114</v>
-      </c>
-      <c r="F38" t="s">
-        <v>18</v>
-      </c>
-      <c r="G38" t="s">
+      <c r="I38" t="s">
         <v>126</v>
-      </c>
-      <c r="H38" t="s">
-        <v>99</v>
-      </c>
-      <c r="I38" t="s">
-        <v>128</v>
       </c>
       <c r="J38">
         <v>5</v>
@@ -2388,78 +2427,78 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B39" t="s">
-        <v>96</v>
+        <v>149</v>
       </c>
       <c r="C39" t="s">
-        <v>97</v>
+        <v>182</v>
       </c>
       <c r="D39" t="s">
-        <v>109</v>
+        <v>183</v>
       </c>
       <c r="E39" t="s">
-        <v>125</v>
+        <v>184</v>
       </c>
       <c r="F39" t="s">
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="G39" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H39" t="s">
-        <v>99</v>
+        <v>185</v>
       </c>
       <c r="I39" t="s">
-        <v>129</v>
+        <v>186</v>
       </c>
       <c r="J39">
         <v>5</v>
+      </c>
+      <c r="K39" t="s">
+        <v>175</v>
+      </c>
+      <c r="L39" t="s">
+        <v>162</v>
+      </c>
+      <c r="M39" t="s">
+        <v>162</v>
+      </c>
+      <c r="N39" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B40" t="s">
-        <v>149</v>
+        <v>93</v>
       </c>
       <c r="C40" t="s">
-        <v>182</v>
+        <v>94</v>
       </c>
       <c r="D40" t="s">
-        <v>183</v>
+        <v>106</v>
       </c>
       <c r="E40" t="s">
-        <v>184</v>
+        <v>122</v>
       </c>
       <c r="F40" t="s">
-        <v>180</v>
+        <v>18</v>
       </c>
       <c r="G40" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H40" t="s">
-        <v>185</v>
+        <v>96</v>
       </c>
       <c r="I40" t="s">
-        <v>186</v>
+        <v>128</v>
       </c>
       <c r="J40">
         <v>5</v>
-      </c>
-      <c r="K40" t="s">
-        <v>175</v>
-      </c>
-      <c r="L40" t="s">
-        <v>162</v>
-      </c>
-      <c r="M40" t="s">
-        <v>162</v>
-      </c>
-      <c r="N40" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.2">
@@ -2467,25 +2506,25 @@
         <v>361</v>
       </c>
       <c r="B41" t="s">
+        <v>93</v>
+      </c>
+      <c r="C41" t="s">
+        <v>94</v>
+      </c>
+      <c r="D41" t="s">
+        <v>129</v>
+      </c>
+      <c r="E41" t="s">
+        <v>130</v>
+      </c>
+      <c r="F41" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" t="s">
+        <v>127</v>
+      </c>
+      <c r="H41" t="s">
         <v>96</v>
-      </c>
-      <c r="C41" t="s">
-        <v>97</v>
-      </c>
-      <c r="D41" t="s">
-        <v>109</v>
-      </c>
-      <c r="E41" t="s">
-        <v>125</v>
-      </c>
-      <c r="F41" t="s">
-        <v>18</v>
-      </c>
-      <c r="G41" t="s">
-        <v>130</v>
-      </c>
-      <c r="H41" t="s">
-        <v>99</v>
       </c>
       <c r="I41" t="s">
         <v>131</v>
@@ -2496,78 +2535,78 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B42" t="s">
-        <v>96</v>
+        <v>149</v>
       </c>
       <c r="C42" t="s">
-        <v>97</v>
+        <v>188</v>
       </c>
       <c r="D42" t="s">
-        <v>132</v>
+        <v>183</v>
       </c>
       <c r="E42" t="s">
-        <v>133</v>
+        <v>184</v>
       </c>
       <c r="F42" t="s">
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="G42" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H42" t="s">
-        <v>99</v>
+        <v>185</v>
       </c>
       <c r="I42" t="s">
-        <v>134</v>
+        <v>189</v>
       </c>
       <c r="J42">
         <v>5</v>
+      </c>
+      <c r="K42" t="s">
+        <v>175</v>
+      </c>
+      <c r="L42" t="s">
+        <v>162</v>
+      </c>
+      <c r="M42" t="s">
+        <v>162</v>
+      </c>
+      <c r="N42" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B43" t="s">
-        <v>149</v>
+        <v>93</v>
       </c>
       <c r="C43" t="s">
-        <v>188</v>
+        <v>94</v>
       </c>
       <c r="D43" t="s">
-        <v>183</v>
+        <v>22</v>
       </c>
       <c r="E43" t="s">
-        <v>184</v>
+        <v>132</v>
       </c>
       <c r="F43" t="s">
-        <v>180</v>
+        <v>18</v>
       </c>
       <c r="G43" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H43" t="s">
-        <v>185</v>
+        <v>96</v>
       </c>
       <c r="I43" t="s">
-        <v>189</v>
+        <v>134</v>
       </c>
       <c r="J43">
         <v>5</v>
-      </c>
-      <c r="K43" t="s">
-        <v>175</v>
-      </c>
-      <c r="L43" t="s">
-        <v>162</v>
-      </c>
-      <c r="M43" t="s">
-        <v>162</v>
-      </c>
-      <c r="N43" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
@@ -2575,13 +2614,13 @@
         <v>365</v>
       </c>
       <c r="B44" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C44" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D44" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="E44" t="s">
         <v>135</v>
@@ -2590,13 +2629,13 @@
         <v>18</v>
       </c>
       <c r="G44" t="s">
+        <v>133</v>
+      </c>
+      <c r="H44" t="s">
+        <v>96</v>
+      </c>
+      <c r="I44" t="s">
         <v>136</v>
-      </c>
-      <c r="H44" t="s">
-        <v>99</v>
-      </c>
-      <c r="I44" t="s">
-        <v>137</v>
       </c>
       <c r="J44">
         <v>5</v>
@@ -2607,28 +2646,28 @@
         <v>365</v>
       </c>
       <c r="B45" t="s">
+        <v>93</v>
+      </c>
+      <c r="C45" t="s">
+        <v>94</v>
+      </c>
+      <c r="D45" t="s">
+        <v>22</v>
+      </c>
+      <c r="E45" t="s">
+        <v>137</v>
+      </c>
+      <c r="F45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" t="s">
+        <v>133</v>
+      </c>
+      <c r="H45" t="s">
         <v>96</v>
       </c>
-      <c r="C45" t="s">
-        <v>97</v>
-      </c>
-      <c r="D45" t="s">
-        <v>109</v>
-      </c>
-      <c r="E45" t="s">
+      <c r="I45" t="s">
         <v>138</v>
-      </c>
-      <c r="F45" t="s">
-        <v>18</v>
-      </c>
-      <c r="G45" t="s">
-        <v>136</v>
-      </c>
-      <c r="H45" t="s">
-        <v>99</v>
-      </c>
-      <c r="I45" t="s">
-        <v>139</v>
       </c>
       <c r="J45">
         <v>5</v>
@@ -2636,78 +2675,78 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B46" t="s">
-        <v>96</v>
+        <v>149</v>
       </c>
       <c r="C46" t="s">
-        <v>97</v>
+        <v>191</v>
       </c>
       <c r="D46" t="s">
-        <v>22</v>
+        <v>118</v>
       </c>
       <c r="E46" t="s">
-        <v>140</v>
+        <v>192</v>
       </c>
       <c r="F46" t="s">
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="G46" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="H46" t="s">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="I46" t="s">
-        <v>141</v>
+        <v>193</v>
       </c>
       <c r="J46">
         <v>5</v>
+      </c>
+      <c r="K46" t="s">
+        <v>175</v>
+      </c>
+      <c r="L46" t="s">
+        <v>194</v>
+      </c>
+      <c r="M46" t="s">
+        <v>195</v>
+      </c>
+      <c r="N46" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B47" t="s">
-        <v>149</v>
+        <v>33</v>
       </c>
       <c r="C47" t="s">
-        <v>191</v>
+        <v>139</v>
       </c>
       <c r="D47" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="E47" t="s">
-        <v>192</v>
+        <v>141</v>
       </c>
       <c r="F47" t="s">
-        <v>180</v>
+        <v>18</v>
       </c>
       <c r="G47" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H47" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I47" t="s">
-        <v>193</v>
+        <v>143</v>
       </c>
       <c r="J47">
         <v>5</v>
-      </c>
-      <c r="K47" t="s">
-        <v>175</v>
-      </c>
-      <c r="L47" t="s">
-        <v>194</v>
-      </c>
-      <c r="M47" t="s">
-        <v>195</v>
-      </c>
-      <c r="N47" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
@@ -2715,13 +2754,13 @@
         <v>368</v>
       </c>
       <c r="B48" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C48" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D48" t="s">
-        <v>143</v>
+        <v>47</v>
       </c>
       <c r="E48" t="s">
         <v>144</v>
@@ -2730,42 +2769,42 @@
         <v>18</v>
       </c>
       <c r="G48" t="s">
+        <v>142</v>
+      </c>
+      <c r="H48" t="s">
+        <v>45</v>
+      </c>
+      <c r="I48" t="s">
         <v>145</v>
       </c>
-      <c r="H48" t="s">
-        <v>48</v>
-      </c>
-      <c r="I48" t="s">
+      <c r="J48">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>369</v>
+      </c>
+      <c r="B49" t="s">
+        <v>50</v>
+      </c>
+      <c r="C49" t="s">
         <v>146</v>
       </c>
-      <c r="J48">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A49">
-        <v>368</v>
-      </c>
-      <c r="B49" t="s">
-        <v>25</v>
-      </c>
-      <c r="C49" t="s">
-        <v>142</v>
-      </c>
       <c r="D49" t="s">
-        <v>50</v>
+        <v>118</v>
       </c>
       <c r="E49" t="s">
+        <v>119</v>
+      </c>
+      <c r="F49" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" t="s">
         <v>147</v>
       </c>
-      <c r="F49" t="s">
-        <v>18</v>
-      </c>
-      <c r="G49" t="s">
-        <v>145</v>
-      </c>
       <c r="H49" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="I49" t="s">
         <v>148</v>
@@ -2774,10 +2813,142 @@
         <v>5</v>
       </c>
     </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>370</v>
+      </c>
+      <c r="B50" t="s">
+        <v>149</v>
+      </c>
+      <c r="C50" t="s">
+        <v>197</v>
+      </c>
+      <c r="D50" t="s">
+        <v>118</v>
+      </c>
+      <c r="E50" t="s">
+        <v>192</v>
+      </c>
+      <c r="F50" t="s">
+        <v>180</v>
+      </c>
+      <c r="G50" t="s">
+        <v>147</v>
+      </c>
+      <c r="H50" t="s">
+        <v>198</v>
+      </c>
+      <c r="I50" t="s">
+        <v>199</v>
+      </c>
+      <c r="J50">
+        <v>5</v>
+      </c>
+      <c r="K50" t="s">
+        <v>175</v>
+      </c>
+      <c r="L50" t="s">
+        <v>200</v>
+      </c>
+      <c r="M50" t="s">
+        <v>201</v>
+      </c>
+      <c r="N50" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>370</v>
+      </c>
+      <c r="B51" t="s">
+        <v>149</v>
+      </c>
+      <c r="C51" t="s">
+        <v>197</v>
+      </c>
+      <c r="D51" t="s">
+        <v>118</v>
+      </c>
+      <c r="E51" t="s">
+        <v>203</v>
+      </c>
+      <c r="F51" t="s">
+        <v>180</v>
+      </c>
+      <c r="G51" t="s">
+        <v>147</v>
+      </c>
+      <c r="H51" t="s">
+        <v>198</v>
+      </c>
+      <c r="I51" t="s">
+        <v>204</v>
+      </c>
+      <c r="J51">
+        <v>5</v>
+      </c>
+      <c r="K51" t="s">
+        <v>175</v>
+      </c>
+      <c r="L51" t="s">
+        <v>200</v>
+      </c>
+      <c r="M51" t="s">
+        <v>205</v>
+      </c>
+      <c r="N51" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>370</v>
+      </c>
+      <c r="B52" t="s">
+        <v>149</v>
+      </c>
+      <c r="C52" t="s">
+        <v>197</v>
+      </c>
+      <c r="D52" t="s">
+        <v>118</v>
+      </c>
+      <c r="E52" t="s">
+        <v>119</v>
+      </c>
+      <c r="F52" t="s">
+        <v>180</v>
+      </c>
+      <c r="G52" t="s">
+        <v>147</v>
+      </c>
+      <c r="H52" t="s">
+        <v>198</v>
+      </c>
+      <c r="I52" t="s">
+        <v>207</v>
+      </c>
+      <c r="J52">
+        <v>5</v>
+      </c>
+      <c r="K52" t="s">
+        <v>175</v>
+      </c>
+      <c r="L52" t="s">
+        <v>208</v>
+      </c>
+      <c r="M52" t="s">
+        <v>209</v>
+      </c>
+      <c r="N52" t="s">
+        <v>210</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N49" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N49">
-      <sortCondition ref="A1:A49"/>
+  <autoFilter ref="A1:N52" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N52">
+      <sortCondition ref="A1:A52"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resumen_trabajos_1.xlsx
+++ b/resumen_trabajos_1.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dacm/we/odoo_con_trabajos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B3DD152-8EF6-C24E-9586-07A1D71B7A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF91CC6-D7A2-6C4C-BB05-619174480A0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2840" yWindow="1460" windowWidth="29420" windowHeight="19320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4180" yWindow="600" windowWidth="29420" windowHeight="19320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$60</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="213">
   <si>
     <t>OT</t>
   </si>
@@ -67,132 +67,22 @@
     <t>Observaciones</t>
   </si>
   <si>
-    <t>Diego Marchant</t>
-  </si>
-  <si>
-    <t>Inspección de contingencias.</t>
-  </si>
-  <si>
-    <t>APR Los Caleos</t>
-  </si>
-  <si>
-    <t>[APR Los Caleos] Pozos y Bombas Elevadoras</t>
+    <t xml:space="preserve">Cristopher Iglesias </t>
+  </si>
+  <si>
+    <t>Avanze instalación solar 2700</t>
+  </si>
+  <si>
+    <t>Los Bronces - Riecillos</t>
+  </si>
+  <si>
+    <t>[Los Bronces - Riecillos] R2700 Gateway</t>
   </si>
   <si>
     <t>ST</t>
   </si>
   <si>
-    <t>09/12/2025</t>
-  </si>
-  <si>
-    <t>Superintendencia de recursos hídricos.</t>
-  </si>
-  <si>
-    <t>Se visita a recinto ya que cliente y operador mencionan no tener actualización de datos, en lo cual se realiza inspección visual de tableros y se percata que luz piloto y equipamientos se encuentran apagados. 
-Se revisó analizador de red de tableros fuerza y se percata que en línea 3 se encuentra con bajo voltaje, 73,6VAC precisamente. 
-Diagnóstico final, recinto se encuentra con una de las fases caída. Durante el día se recuperó recinto por parte de distribuidor eléctrico de la zona, obteniendo estabilidad de voltaje en la red eléctrica en sus 3 fases.</t>
-  </si>
-  <si>
-    <t>Gestión Hídrica El Soldado</t>
-  </si>
-  <si>
-    <t>[Gestión Hídrica El Soldado] Pozo El Melón N° 02 (PEM-02) Gateway A</t>
-  </si>
-  <si>
-    <t>Se visita recinto para presenciar trabajos avanzados en pozo, en lo cual, aún sigue sin conectarse a las red matriz, lo que explica el aún no presencia de red eléctrica en el recinto.
-Pozo aún se encuentra en periodo de mantenimiento.</t>
-  </si>
-  <si>
-    <t>Juan José López</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validación de variables </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calidad de aguas </t>
-  </si>
-  <si>
-    <t>Recinto PME-09, P6 Dren Muro Este</t>
-  </si>
-  <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t>10/12/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patricio Cortes </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se realiza revicion de variables en los recintos </t>
-  </si>
-  <si>
-    <t>Elías Sanchez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Traslado de materiales </t>
-  </si>
-  <si>
-    <t>Los Bronces - Riecillos</t>
-  </si>
-  <si>
-    <t>[Los Bronces - Riecillos] R2700 Gateway</t>
-  </si>
-  <si>
     <t>11/12/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paula Riquelme </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se realiza apoyo a camión pluma de GeoBarra para traslado de andamio hasta sala de bombas 2700. Se hace entrega de estructura andamio para su montaje por parte de empresa San Isidro.
-Posterior a eso se acude con mismo camión de GeoBarra a Patio de tuberías para poder llevar paneles fotovoltaicos pero no es factible ya que deben estar paletizados con zunchos.
-Finalmente se trasladaron baterías 200AH (2), accesorios para montaje de estructura fotovoltaica, inversor Epever y tablero We para aprovechar la cercanía al sector de riecillos, almacenando en sala de bombas 2700.
-Se inspecciona montaje de estructura del andamio con apr y se toman medidas de la zona de trabajo
-- Losa ancho 4.60mts
-- Largo 12 mts
-Observaciones 
-Faltan uniones (12) para rieles de la estructura fotovoltaica se adjuntan imágenes </t>
-  </si>
-  <si>
-    <t>Evaluación de trabajos y mantenimiento.</t>
-  </si>
-  <si>
-    <t>Se realiza evaluación de trabajos para efectuar traslado de gateway de PEM-02 hacia Caseta El Melón, debido al mantenimiento prolongado en PEM-02 y pérdida de transmisión de datos en plataforma, en lo cual, para comenzar a ejecutar dichas labores, se debe contar con escalera con plataforma, ya que es factible dicho cambio.</t>
-  </si>
-  <si>
-    <t>Actualización de datos en softwares</t>
-  </si>
-  <si>
-    <t>[Gestión Hídrica El Soldado] Pozo El Melón N° 06 (PEM-06) Nodo</t>
-  </si>
-  <si>
-    <t>05/12/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Superintendencia de recursos hidricos </t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEM-06
-Ajuste a zero de sensor en software control center series
-Los pulsos y totalizador se actualizan en toolbox
-Se rescatan y actualizan datos de sensor hidrostatico y se actualiza planilla Excel con datos del punto </t>
-  </si>
-  <si>
-    <t>AAES</t>
-  </si>
-  <si>
-    <t>PI17 AL PI20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se realiza inspección general de los puntos PI17, 18, 19 y 20.
-Se encuentra fuga en el punto PI20 por el lado de radier del pozo. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cristopher Iglesias </t>
-  </si>
-  <si>
-    <t>Avanze instalación solar 2700</t>
   </si>
   <si>
     <t>Paula Riquelme</t>
@@ -204,13 +94,22 @@
 Ademas se realiza la ultima inspección del andamiaje armado en la sala, esta vez se analiza la estructura superior luego d ela mejora implementada por la empresa San Isidro.</t>
   </si>
   <si>
+    <t>Elías Sanchez</t>
+  </si>
+  <si>
     <t>Traslado gateway</t>
   </si>
   <si>
+    <t>Gestión Hídrica El Soldado</t>
+  </si>
+  <si>
     <t>[Gestión Hídrica El Soldado] Pozos El Soldado Caseta el Melón</t>
   </si>
   <si>
     <t>15/12/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Superintendencia de recursos hidricos </t>
   </si>
   <si>
     <t xml:space="preserve">Se realiza retiro de antena Gateway del recinto PEM-02 para trasladarlo e instalar en el punto de Caseta el Melón.
@@ -222,6 +121,9 @@
   </si>
   <si>
     <t>16/12/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paula Riquelme </t>
   </si>
   <si>
     <t xml:space="preserve">Traslado final de materiales restantes de patio de tuberias a 3050 y perfil a 2700. Izaje de materiales a loza superior con apoyo de camion pluma.
@@ -289,9 +191,6 @@
   </si>
   <si>
     <t>Mantenimiento - soporte</t>
-  </si>
-  <si>
-    <t>19/12/2025</t>
   </si>
   <si>
     <t xml:space="preserve">Caseta el melon
@@ -346,7 +245,7 @@
     <t>BN12</t>
   </si>
   <si>
-    <t>23/12/2025</t>
+    <t>LT</t>
   </si>
   <si>
     <t xml:space="preserve">Se obtienen permisos de trabajo para rondas diarias de la semana y la implementación de telemetria en el punto BN12. 
@@ -386,6 +285,9 @@
     <t>[ASP Pozos] Pozo 24</t>
   </si>
   <si>
+    <t>23/12/2025</t>
+  </si>
+  <si>
     <t>Aguas Santiago Poniente</t>
   </si>
   <si>
@@ -425,7 +327,7 @@
     <t>[Gestión Hídrica El Soldado] Pozo Los Litres N° 01 (PLL-01) Nodo A12</t>
   </si>
   <si>
-    <t>25/12/2025</t>
+    <t>24/12/2025</t>
   </si>
   <si>
     <t xml:space="preserve">Realizamos mantenimiento preventivo,  limpieza de tableros, reapriete de terminales.
@@ -451,9 +353,6 @@
     <t>[Global Tórtolas] Pozo BN12</t>
   </si>
   <si>
-    <t>24/12/2025</t>
-  </si>
-  <si>
     <t xml:space="preserve">Se finaliza el conexionado telemetria del pozo BN12 dejando el punto debidamente alimentado. Junto con el apoyo electrico de AA se hace el desbloqueo del tablero y la entrega del área de trabajo.
 </t>
   </si>
@@ -493,7 +392,7 @@
     <t>[Gestión Hídrica El Soldado] PM-3 Nodo B19</t>
   </si>
   <si>
-    <t>01/01/2026</t>
+    <t>31/12/2025</t>
   </si>
   <si>
     <t xml:space="preserve">Por aviso de oficina procedemos ir al punto a recetear el tablero ya que se encontraba la sonda dando datos erróneo. </t>
@@ -527,6 +426,9 @@
   <si>
     <t>Se acude al punto a verificar la condición y se anota lo que falta para la habilitación de éste.
 Batería acorde y peinado de cables</t>
+  </si>
+  <si>
+    <t>AAES</t>
   </si>
   <si>
     <t>Gestiones</t>
@@ -549,87 +451,124 @@
 Adicionalmente se instalan equipos de comunicación para la lectura de datos a través de red LORA.</t>
   </si>
   <si>
+    <t>[Gestión Hídrica El Soldado] Pozo El Melón N° 01 (PEM-01) Nodo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visita a Pem 01 con SS
+Se debe entregar a SS estructura de soporte para panel
+ dimensiones : 1217*992*35mm
+Se acude para verificar el posicionamiento del poste a instalar. </t>
+  </si>
+  <si>
+    <t>[Gestión Hídrica El Soldado] Pozo El Melón N° 03 (PEM-03)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visita a Pem 03 con SS
+Se debe entregar a SS estructura de soporte para panel y un panel solar, ya que fue vandalizado. 
+ dimensiones panel : 1217*992*35mm
+Se acude para verificar el posicionamiento del poste a instalar. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Válvula desde piscina UG hacia piscina 3800 </t>
+  </si>
+  <si>
+    <t>Se acude al punto para cerrar válvula por completo por solicitud del cliente</t>
+  </si>
+  <si>
+    <t>Mantenimiento correctivo R2700</t>
+  </si>
+  <si>
+    <t>07/01/2026</t>
+  </si>
+  <si>
+    <t>En la visita a terreno se constata que la caida de la telemetria se debe a la desnergizacion de antena starlink, esto ultimo por activación de interruptor automático.
+Se regulariza la condición y adicionalmente se integra la UPS al circuito de alimentación conectando entrada en tablero de paso existente y su salida aguas arriba a automático general telemetría. 
+De esta forma si la red electerica cae, la UPS continuará entregandole energia al sistema completo, una vez la UPS se agote, el inversor continua alimentando con baterias y solución solar.
+Queda pendiente en sala R2700 instalar gabinete para remontar 2 baterias de 100AH y conectarlas al sistema de respaldo.
+Instalación de conectores MC4 paralelo para regularizar la conexión fisica de los paneles.
+Instalar automático DC para la protección de banco de baterías.
+Regularizar terminales en cables de alimentación solar y baterías (requiere ferrules) cable 6AWG.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se acude al punto para resolución de ticket, ya que presentaba peaks de valores respecto a la conductividaddel agua en plataforma.
+Se revisan software y se verifica la lectura
+Se encuentra en orden y registrando valores en plataforma. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garantía pantalla sala de control </t>
+  </si>
+  <si>
+    <t>Sala de control LPG</t>
+  </si>
+  <si>
+    <t>Sala de control</t>
+  </si>
+  <si>
+    <t>08/01/2026</t>
+  </si>
+  <si>
+    <t>Hernan Rojas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se realiza instalación de nueva pantalla por garantia </t>
+  </si>
+  <si>
+    <t>Implementacion red LORA WAN</t>
+  </si>
+  <si>
+    <t>[Global Tórtolas] Pozo BN3</t>
+  </si>
+  <si>
+    <t>Se instala equipos y antena para monitoreo de datos a través de red lora con éxito.</t>
+  </si>
+  <si>
+    <t>[Global Tórtolas] Pozo BN4</t>
+  </si>
+  <si>
+    <t>[Global Tórtolas] Pozo O4B</t>
+  </si>
+  <si>
+    <t>Se instala equipos y antena para monitoreo de datos a través de red lora con éxito.
+Queda pendiente validación de datos ya que punto se encuentra desnergizado.</t>
+  </si>
+  <si>
+    <t>[Global Tórtolas] Pozo O4</t>
+  </si>
+  <si>
+    <t>Se instala equipos y antena para monitoreo de datos a través de red lora con éxito.
+Queda pendiente validación de datos ya que punto se encuentra desnergizado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planta Solar </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se acude a revisión de los pozos de inyección del 17 al 20.
+Se contrasta Caudal en terreno y en plataforma siendo estos 4 puntos coherentes y valores correctos
+Se revisa planta Solar y se limpian paneles para evitar algún tipo de falla respectivamente.
+Observaciones
+PI-17 se destraba válvula vortex y continua su funcionamiento normal.
+</t>
+  </si>
+  <si>
+    <t>APR Los Caleos</t>
+  </si>
+  <si>
+    <t>[APR Los Caleos] Pozo 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se acude a revisar el pozo 4 de los caleos por la falla que tuvo el día de ayer, hablamos con el operador y comento que hoy le paso algo parecido y volvió la señal, también hace unas semanas en un turno de noche como 3 veces. Asique fuimos al punto con el para ver la situación 
+- Tablero We connect presenta muy alta temperatura en teltonika y en el tablero en general, tablero no cuenta con ventilación 
+- Fuente de voltaje estaba en 28,40v se reduce a 26,20, por sobrecalentamiento, se observa que potenciómetro de voltaje de la fuente esta hundido hacia dentro y se hace difícil regular.
+Son indicios para pensar en reemplazar la fuente y quizás una mejora en sentido de ventilación o enfriamiento del tablero. </t>
+  </si>
+  <si>
     <t>Ángel Zamora</t>
   </si>
   <si>
-    <t>[Global Tórtolas] Pozo BN3</t>
-  </si>
-  <si>
-    <t>MC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fimar de pt ok.
-Traspaso de área por dueño de zona stp ok.
-Documentos pt, det y aisalación y bloqueo ok y validados.
-Cambio de sensor ok.
-Validación de datos en plataforma y terreno ok.
-</t>
-  </si>
-  <si>
-    <t>Sensor de Nivel</t>
-  </si>
-  <si>
-    <t>Flux 0-10 bar 80 mts</t>
-  </si>
-  <si>
-    <t>159367</t>
-  </si>
-  <si>
-    <t>Pozo BN03 queda enviando datos de nivel ok. 
-Validación terreno y plataforma ok.
-Sin observaciones.</t>
-  </si>
-  <si>
-    <t>[Gestión Hídrica El Soldado] Pozo El Melón N° 03 (PEM-03)</t>
+    <t xml:space="preserve">Mantenimiento Preventivo </t>
   </si>
   <si>
     <t>MP</t>
-  </si>
-  <si>
-    <t>Se realiza mantenimiento preventivo a recinto completo, limpieza y re apriete de tableros, actualización de volumen en caudalimetro y validación de datos nivel en terreno, no se pudo validar con plataforma ya que gateway el melón no se encuentra operativo, pero se valida con pozometro y dato obtenido en UC-300 obteniendo una diferencia de 10cm de nivel.
-Datos obtenidos en terreno:
-Nivel pozometro: 9,1m
-UC-300: 4,39 bar / 9,2m transformado.
-Falta panel fotovoltaico ya que con anterioridad fue usurpado.</t>
-  </si>
-  <si>
-    <t>Tablero</t>
-  </si>
-  <si>
-    <t>Tablero nodo lora</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Tablero nodo lora inicialmente era configuración 220VAC pero se realiza cambio a energía solar VDC por falta de disponibilidad red eléctrica. Este cambio se realizó al momento de instalación.</t>
-  </si>
-  <si>
-    <t>Caudalímetro Mecánico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mecánico </t>
-  </si>
-  <si>
-    <t>N/a</t>
-  </si>
-  <si>
-    <t>DN: 80</t>
-  </si>
-  <si>
-    <t>Keller PR-36XS</t>
-  </si>
-  <si>
-    <t>1262272</t>
-  </si>
-  <si>
-    <t>S/O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mantenimiento Preventivo </t>
-  </si>
-  <si>
-    <t>[Gestión Hídrica El Soldado] Pozo El Melón N° 01 (PEM-01) Nodo</t>
   </si>
   <si>
     <t xml:space="preserve">Nicolas Valenzuela </t>
@@ -646,6 +585,9 @@
   </si>
   <si>
     <t>23306373</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
   <si>
     <t>Integración Red Lora</t>
@@ -759,6 +701,78 @@
   </si>
   <si>
     <t>Punto con transmisión de datos ok.</t>
+  </si>
+  <si>
+    <t>[Gestión Hídrica El Soldado] PM-28C Nodo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se realiza limpieza de los tableros, reapriete de terminales, mediciones de voltaje, sopletiado, limpieza de panel fotovoltaico, revisión de software ecostruxture y toolbox, verificación y contratación de variables en plataforma, limpieza de sonda multiparamétrica y sensor hidrostatico. </t>
+  </si>
+  <si>
+    <t>Tablero</t>
+  </si>
+  <si>
+    <t>1 tablero fotovoltaico + uc300
+1 tablero PLC 16R</t>
+  </si>
+  <si>
+    <t>...</t>
+  </si>
+  <si>
+    <t>Falta rotular tableros con código qr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panel fotovoltaico </t>
+  </si>
+  <si>
+    <t xml:space="preserve">... </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se realiza la limpieza de panel fotovoltaico 
+No presenta observaciones
+</t>
+  </si>
+  <si>
+    <t>[Gestión Hídrica El Soldado] PM-30 Nodo</t>
+  </si>
+  <si>
+    <t>- Tablero PLC 16R
+- Tablero fotovoltaico + UC300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No se presentan observaciones </t>
+  </si>
+  <si>
+    <t>Panel fotovoltsico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se realiza limpieza
+No presenta observaciones </t>
+  </si>
+  <si>
+    <t>Thinkpad lenovo</t>
+  </si>
+  <si>
+    <t>V30F882K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reposición pantalla dañada </t>
+  </si>
+  <si>
+    <t>[Gestión Hídrica El Soldado] PM-07 Gateway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se realiza limpieza de tableros, limpieza de panel fotovoltaico, reapriete de terminales, mediciones de voltaje, revisión, contratación y validación de datos en plataforma y software ecostruxture.
+Datos congruentes. 
+</t>
+  </si>
+  <si>
+    <t>Tablero de banco baterias
+Tablero We connect
+Tablero PLC16R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No presenta observaciones </t>
   </si>
 </sst>
 </file>
@@ -1122,7 +1136,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N52"/>
+  <dimension ref="A1:N60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
@@ -1171,39 +1185,51 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>150</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>151</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>121</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>152</v>
       </c>
       <c r="G2" t="s">
         <v>19</v>
       </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="I2" t="s">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="J2">
         <v>5</v>
+      </c>
+      <c r="K2" t="s">
+        <v>155</v>
+      </c>
+      <c r="L2" t="s">
+        <v>156</v>
+      </c>
+      <c r="M2" t="s">
+        <v>157</v>
+      </c>
+      <c r="N2" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -1212,10 +1238,10 @@
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -1227,7 +1253,7 @@
         <v>20</v>
       </c>
       <c r="I3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J3">
         <v>5</v>
@@ -1235,31 +1261,31 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
         <v>25</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" t="s">
         <v>26</v>
       </c>
-      <c r="D4" t="s">
+      <c r="H4" t="s">
         <v>27</v>
       </c>
-      <c r="E4" t="s">
+      <c r="I4" t="s">
         <v>28</v>
-      </c>
-      <c r="F4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" t="s">
-        <v>32</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -1267,107 +1293,107 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="B5" t="s">
-        <v>149</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>118</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>150</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>151</v>
+        <v>18</v>
       </c>
       <c r="G5" t="s">
         <v>30</v>
       </c>
       <c r="H5" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I5" t="s">
-        <v>152</v>
+        <v>32</v>
       </c>
       <c r="J5">
         <v>5</v>
-      </c>
-      <c r="K5" t="s">
-        <v>153</v>
-      </c>
-      <c r="L5" t="s">
-        <v>154</v>
-      </c>
-      <c r="M5" t="s">
-        <v>155</v>
-      </c>
-      <c r="N5" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>150</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>159</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>160</v>
       </c>
       <c r="F6" t="s">
-        <v>18</v>
+        <v>161</v>
       </c>
       <c r="G6" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="H6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I6" t="s">
-        <v>39</v>
+        <v>162</v>
       </c>
       <c r="J6">
         <v>5</v>
+      </c>
+      <c r="K6" t="s">
+        <v>155</v>
+      </c>
+      <c r="L6" t="s">
+        <v>158</v>
+      </c>
+      <c r="M6" t="s">
+        <v>158</v>
+      </c>
+      <c r="N6" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
       </c>
       <c r="G7" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="H7" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="J7">
         <v>5</v>
@@ -1375,160 +1401,124 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E8" t="s">
-        <v>157</v>
+        <v>37</v>
       </c>
       <c r="F8" t="s">
-        <v>158</v>
+        <v>18</v>
       </c>
       <c r="G8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H8" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I8" t="s">
-        <v>159</v>
+        <v>39</v>
       </c>
       <c r="J8">
         <v>5</v>
-      </c>
-      <c r="K8" t="s">
-        <v>160</v>
-      </c>
-      <c r="L8" t="s">
-        <v>161</v>
-      </c>
-      <c r="M8" t="s">
-        <v>162</v>
-      </c>
-      <c r="N8" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
         <v>40</v>
       </c>
-      <c r="D9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" t="s">
-        <v>157</v>
-      </c>
       <c r="F9" t="s">
-        <v>158</v>
+        <v>18</v>
       </c>
       <c r="G9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H9" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I9" t="s">
-        <v>159</v>
+        <v>41</v>
       </c>
       <c r="J9">
         <v>5</v>
-      </c>
-      <c r="K9" t="s">
-        <v>164</v>
-      </c>
-      <c r="L9" t="s">
-        <v>165</v>
-      </c>
-      <c r="M9" t="s">
-        <v>166</v>
-      </c>
-      <c r="N9" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>157</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
-        <v>158</v>
+        <v>18</v>
       </c>
       <c r="G10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H10" t="s">
         <v>20</v>
       </c>
       <c r="I10" t="s">
-        <v>159</v>
+        <v>43</v>
       </c>
       <c r="J10">
         <v>5</v>
-      </c>
-      <c r="K10" t="s">
-        <v>153</v>
-      </c>
-      <c r="L10" t="s">
-        <v>168</v>
-      </c>
-      <c r="M10" t="s">
-        <v>169</v>
-      </c>
-      <c r="N10" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
       </c>
       <c r="G11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H11" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="I11" t="s">
         <v>46</v>
@@ -1539,31 +1529,31 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12" t="s">
         <v>48</v>
-      </c>
-      <c r="F12" t="s">
-        <v>18</v>
-      </c>
-      <c r="G12" t="s">
-        <v>44</v>
-      </c>
-      <c r="H12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I12" t="s">
-        <v>49</v>
       </c>
       <c r="J12">
         <v>5</v>
@@ -1571,75 +1561,63 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="B13" t="s">
-        <v>149</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>171</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>172</v>
+        <v>49</v>
       </c>
       <c r="F13" t="s">
-        <v>158</v>
+        <v>18</v>
       </c>
       <c r="G13" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H13" t="s">
-        <v>173</v>
+        <v>27</v>
       </c>
       <c r="I13" t="s">
-        <v>174</v>
+        <v>50</v>
       </c>
       <c r="J13">
         <v>5</v>
-      </c>
-      <c r="K13" t="s">
-        <v>175</v>
-      </c>
-      <c r="L13" t="s">
-        <v>176</v>
-      </c>
-      <c r="M13" t="s">
-        <v>177</v>
-      </c>
-      <c r="N13" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="E14" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="F14" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="G14" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="H14" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="I14" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="J14">
         <v>5</v>
@@ -1647,31 +1625,31 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="E15" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F15" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="G15" t="s">
         <v>56</v>
       </c>
       <c r="H15" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="I15" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="J15">
         <v>5</v>
@@ -1679,31 +1657,31 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D16" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="E16" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
       </c>
       <c r="G16" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H16" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I16" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J16">
         <v>5</v>
@@ -1711,75 +1689,63 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="B17" t="s">
-        <v>149</v>
+        <v>64</v>
       </c>
       <c r="C17" t="s">
-        <v>178</v>
+        <v>65</v>
       </c>
       <c r="D17" t="s">
-        <v>118</v>
+        <v>24</v>
       </c>
       <c r="E17" t="s">
-        <v>179</v>
+        <v>66</v>
       </c>
       <c r="F17" t="s">
-        <v>180</v>
+        <v>18</v>
       </c>
       <c r="G17" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="H17" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="I17" t="s">
-        <v>181</v>
+        <v>68</v>
       </c>
       <c r="J17">
         <v>5</v>
-      </c>
-      <c r="K17" t="s">
-        <v>175</v>
-      </c>
-      <c r="L17" t="s">
-        <v>162</v>
-      </c>
-      <c r="M17" t="s">
-        <v>162</v>
-      </c>
-      <c r="N17" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C18" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D18" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="E18" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="F18" t="s">
         <v>18</v>
       </c>
       <c r="G18" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="H18" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="I18" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="J18">
         <v>5</v>
@@ -1787,31 +1753,31 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="D19" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="E19" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="F19" t="s">
         <v>18</v>
       </c>
       <c r="G19" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H19" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="I19" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="J19">
         <v>5</v>
@@ -1819,31 +1785,31 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="C20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D20" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="E20" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="F20" t="s">
         <v>18</v>
       </c>
       <c r="G20" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H20" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="I20" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="J20">
         <v>5</v>
@@ -1851,31 +1817,31 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="C21" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D21" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E21" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="F21" t="s">
         <v>18</v>
       </c>
       <c r="G21" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H21" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="I21" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="J21">
         <v>5</v>
@@ -1883,31 +1849,31 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="C22" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D22" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E22" t="s">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="F22" t="s">
         <v>18</v>
       </c>
       <c r="G22" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H22" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="I22" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="J22">
         <v>5</v>
@@ -1915,31 +1881,31 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D23" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="E23" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="F23" t="s">
         <v>18</v>
       </c>
       <c r="G23" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="H23" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="I23" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J23">
         <v>5</v>
@@ -1947,31 +1913,31 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="D24" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E24" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="F24" t="s">
         <v>18</v>
       </c>
       <c r="G24" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H24" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="I24" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J24">
         <v>5</v>
@@ -1979,31 +1945,31 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="C25" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="D25" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E25" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="F25" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="G25" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="H25" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="I25" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="J25">
         <v>5</v>
@@ -2011,31 +1977,31 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="C26" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="D26" t="s">
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="E26" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F26" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="G26" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H26" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="I26" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="J26">
         <v>5</v>
@@ -2043,31 +2009,31 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="C27" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="D27" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E27" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F27" t="s">
         <v>18</v>
       </c>
       <c r="G27" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H27" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="I27" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J27">
         <v>5</v>
@@ -2075,63 +2041,75 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>150</v>
       </c>
       <c r="C28" t="s">
+        <v>163</v>
+      </c>
+      <c r="D28" t="s">
+        <v>164</v>
+      </c>
+      <c r="E28" t="s">
+        <v>165</v>
+      </c>
+      <c r="F28" t="s">
+        <v>161</v>
+      </c>
+      <c r="G28" t="s">
         <v>94</v>
       </c>
-      <c r="D28" t="s">
-        <v>22</v>
-      </c>
-      <c r="E28" t="s">
-        <v>95</v>
-      </c>
-      <c r="F28" t="s">
-        <v>18</v>
-      </c>
-      <c r="G28" t="s">
-        <v>85</v>
-      </c>
       <c r="H28" t="s">
-        <v>96</v>
+        <v>166</v>
       </c>
       <c r="I28" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
       <c r="J28">
         <v>5</v>
+      </c>
+      <c r="K28" t="s">
+        <v>155</v>
+      </c>
+      <c r="L28" t="s">
+        <v>158</v>
+      </c>
+      <c r="M28" t="s">
+        <v>158</v>
+      </c>
+      <c r="N28" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="B29" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="C29" t="s">
+        <v>65</v>
+      </c>
+      <c r="D29" t="s">
+        <v>78</v>
+      </c>
+      <c r="E29" t="s">
+        <v>93</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" t="s">
         <v>98</v>
       </c>
-      <c r="D29" t="s">
+      <c r="H29" t="s">
+        <v>67</v>
+      </c>
+      <c r="I29" t="s">
         <v>99</v>
-      </c>
-      <c r="E29" t="s">
-        <v>100</v>
-      </c>
-      <c r="F29" t="s">
-        <v>18</v>
-      </c>
-      <c r="G29" t="s">
-        <v>91</v>
-      </c>
-      <c r="H29" t="s">
-        <v>101</v>
-      </c>
-      <c r="I29" t="s">
-        <v>102</v>
       </c>
       <c r="J29">
         <v>5</v>
@@ -2139,31 +2117,31 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="B30" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="C30" t="s">
-        <v>103</v>
+        <v>65</v>
       </c>
       <c r="D30" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E30" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F30" t="s">
         <v>18</v>
       </c>
       <c r="G30" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="H30" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="I30" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="J30">
         <v>5</v>
@@ -2171,63 +2149,75 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>150</v>
       </c>
       <c r="C31" t="s">
-        <v>94</v>
+        <v>169</v>
       </c>
       <c r="D31" t="s">
-        <v>106</v>
+        <v>164</v>
       </c>
       <c r="E31" t="s">
-        <v>107</v>
+        <v>165</v>
       </c>
       <c r="F31" t="s">
-        <v>18</v>
+        <v>161</v>
       </c>
       <c r="G31" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="H31" t="s">
-        <v>96</v>
+        <v>166</v>
       </c>
       <c r="I31" t="s">
-        <v>108</v>
+        <v>170</v>
       </c>
       <c r="J31">
         <v>5</v>
+      </c>
+      <c r="K31" t="s">
+        <v>155</v>
+      </c>
+      <c r="L31" t="s">
+        <v>158</v>
+      </c>
+      <c r="M31" t="s">
+        <v>158</v>
+      </c>
+      <c r="N31" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="C32" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="D32" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E32" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="F32" t="s">
         <v>18</v>
       </c>
       <c r="G32" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="H32" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="I32" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="J32">
         <v>5</v>
@@ -2235,31 +2225,31 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="C33" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="D33" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="E33" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F33" t="s">
         <v>18</v>
       </c>
       <c r="G33" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="H33" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="I33" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="J33">
         <v>5</v>
@@ -2267,31 +2257,31 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="C34" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="D34" t="s">
-        <v>106</v>
+        <v>24</v>
       </c>
       <c r="E34" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="F34" t="s">
         <v>18</v>
       </c>
       <c r="G34" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="H34" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="I34" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="J34">
         <v>5</v>
@@ -2299,63 +2289,75 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="B35" t="s">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="C35" t="s">
-        <v>117</v>
+        <v>172</v>
       </c>
       <c r="D35" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="E35" t="s">
-        <v>119</v>
+        <v>173</v>
       </c>
       <c r="F35" t="s">
-        <v>18</v>
+        <v>161</v>
       </c>
       <c r="G35" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="H35" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I35" t="s">
-        <v>121</v>
+        <v>174</v>
       </c>
       <c r="J35">
         <v>5</v>
+      </c>
+      <c r="K35" t="s">
+        <v>155</v>
+      </c>
+      <c r="L35" t="s">
+        <v>175</v>
+      </c>
+      <c r="M35" t="s">
+        <v>176</v>
+      </c>
+      <c r="N35" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="B36" t="s">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="C36" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="D36" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E36" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="F36" t="s">
         <v>18</v>
       </c>
       <c r="G36" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="H36" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="I36" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="J36">
         <v>5</v>
@@ -2363,31 +2365,31 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="B37" t="s">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="C37" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="D37" t="s">
-        <v>22</v>
+        <v>115</v>
       </c>
       <c r="E37" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F37" t="s">
         <v>18</v>
       </c>
       <c r="G37" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="H37" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="I37" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="J37">
         <v>5</v>
@@ -2395,31 +2397,31 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="B38" t="s">
-        <v>93</v>
+        <v>14</v>
       </c>
       <c r="C38" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="D38" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E38" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="F38" t="s">
         <v>18</v>
       </c>
       <c r="G38" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H38" t="s">
-        <v>96</v>
+        <v>31</v>
       </c>
       <c r="I38" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="J38">
         <v>5</v>
@@ -2427,183 +2429,195 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="B39" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C39" t="s">
+        <v>178</v>
+      </c>
+      <c r="D39" t="s">
+        <v>90</v>
+      </c>
+      <c r="E39" t="s">
+        <v>173</v>
+      </c>
+      <c r="F39" t="s">
+        <v>161</v>
+      </c>
+      <c r="G39" t="s">
+        <v>119</v>
+      </c>
+      <c r="H39" t="s">
+        <v>179</v>
+      </c>
+      <c r="I39" t="s">
+        <v>180</v>
+      </c>
+      <c r="J39">
+        <v>5</v>
+      </c>
+      <c r="K39" t="s">
+        <v>155</v>
+      </c>
+      <c r="L39" t="s">
+        <v>181</v>
+      </c>
+      <c r="M39" t="s">
         <v>182</v>
       </c>
-      <c r="D39" t="s">
+      <c r="N39" t="s">
         <v>183</v>
-      </c>
-      <c r="E39" t="s">
-        <v>184</v>
-      </c>
-      <c r="F39" t="s">
-        <v>180</v>
-      </c>
-      <c r="G39" t="s">
-        <v>127</v>
-      </c>
-      <c r="H39" t="s">
-        <v>185</v>
-      </c>
-      <c r="I39" t="s">
-        <v>186</v>
-      </c>
-      <c r="J39">
-        <v>5</v>
-      </c>
-      <c r="K39" t="s">
-        <v>175</v>
-      </c>
-      <c r="L39" t="s">
-        <v>162</v>
-      </c>
-      <c r="M39" t="s">
-        <v>162</v>
-      </c>
-      <c r="N39" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="B40" t="s">
-        <v>93</v>
+        <v>150</v>
       </c>
       <c r="C40" t="s">
-        <v>94</v>
+        <v>178</v>
       </c>
       <c r="D40" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E40" t="s">
-        <v>122</v>
+        <v>184</v>
       </c>
       <c r="F40" t="s">
-        <v>18</v>
+        <v>161</v>
       </c>
       <c r="G40" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="H40" t="s">
-        <v>96</v>
+        <v>179</v>
       </c>
       <c r="I40" t="s">
-        <v>128</v>
+        <v>185</v>
       </c>
       <c r="J40">
         <v>5</v>
+      </c>
+      <c r="K40" t="s">
+        <v>155</v>
+      </c>
+      <c r="L40" t="s">
+        <v>181</v>
+      </c>
+      <c r="M40" t="s">
+        <v>186</v>
+      </c>
+      <c r="N40" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="B41" t="s">
-        <v>93</v>
+        <v>150</v>
       </c>
       <c r="C41" t="s">
-        <v>94</v>
+        <v>178</v>
       </c>
       <c r="D41" t="s">
-        <v>129</v>
+        <v>90</v>
       </c>
       <c r="E41" t="s">
-        <v>130</v>
+        <v>91</v>
       </c>
       <c r="F41" t="s">
-        <v>18</v>
+        <v>161</v>
       </c>
       <c r="G41" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="H41" t="s">
-        <v>96</v>
+        <v>179</v>
       </c>
       <c r="I41" t="s">
-        <v>131</v>
+        <v>188</v>
       </c>
       <c r="J41">
         <v>5</v>
+      </c>
+      <c r="K41" t="s">
+        <v>155</v>
+      </c>
+      <c r="L41" t="s">
+        <v>189</v>
+      </c>
+      <c r="M41" t="s">
+        <v>190</v>
+      </c>
+      <c r="N41" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="B42" t="s">
-        <v>149</v>
+        <v>22</v>
       </c>
       <c r="C42" t="s">
-        <v>188</v>
+        <v>65</v>
       </c>
       <c r="D42" t="s">
-        <v>183</v>
+        <v>24</v>
       </c>
       <c r="E42" t="s">
-        <v>184</v>
+        <v>121</v>
       </c>
       <c r="F42" t="s">
-        <v>180</v>
+        <v>62</v>
       </c>
       <c r="G42" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="H42" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="I42" t="s">
-        <v>189</v>
+        <v>122</v>
       </c>
       <c r="J42">
         <v>5</v>
-      </c>
-      <c r="K42" t="s">
-        <v>175</v>
-      </c>
-      <c r="L42" t="s">
-        <v>162</v>
-      </c>
-      <c r="M42" t="s">
-        <v>162</v>
-      </c>
-      <c r="N42" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="B43" t="s">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="C43" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="D43" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E43" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="F43" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="G43" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="H43" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="I43" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="J43">
         <v>5</v>
@@ -2611,31 +2625,31 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="B44" t="s">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="C44" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="D44" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="E44" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="F44" t="s">
         <v>18</v>
       </c>
       <c r="G44" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="H44" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="I44" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="J44">
         <v>5</v>
@@ -2643,60 +2657,72 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="B45" t="s">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="C45" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="D45" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E45" t="s">
-        <v>137</v>
+        <v>192</v>
       </c>
       <c r="F45" t="s">
-        <v>18</v>
+        <v>152</v>
       </c>
       <c r="G45" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="H45" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="I45" t="s">
-        <v>138</v>
+        <v>193</v>
       </c>
       <c r="J45">
         <v>5</v>
+      </c>
+      <c r="K45" t="s">
+        <v>194</v>
+      </c>
+      <c r="L45" t="s">
+        <v>195</v>
+      </c>
+      <c r="M45" t="s">
+        <v>196</v>
+      </c>
+      <c r="N45" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="B46" t="s">
-        <v>149</v>
+        <v>22</v>
       </c>
       <c r="C46" t="s">
-        <v>191</v>
+        <v>65</v>
       </c>
       <c r="D46" t="s">
-        <v>118</v>
+        <v>24</v>
       </c>
       <c r="E46" t="s">
         <v>192</v>
       </c>
       <c r="F46" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="G46" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="H46" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="I46" t="s">
         <v>193</v>
@@ -2705,45 +2731,45 @@
         <v>5</v>
       </c>
       <c r="K46" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="L46" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="M46" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="N46" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B47" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C47" t="s">
-        <v>139</v>
+        <v>65</v>
       </c>
       <c r="D47" t="s">
-        <v>140</v>
+        <v>24</v>
       </c>
       <c r="E47" t="s">
-        <v>141</v>
+        <v>103</v>
       </c>
       <c r="F47" t="s">
         <v>18</v>
       </c>
       <c r="G47" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="H47" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="I47" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="J47">
         <v>5</v>
@@ -2751,204 +2777,481 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B48" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C48" t="s">
-        <v>139</v>
+        <v>65</v>
       </c>
       <c r="D48" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="E48" t="s">
-        <v>144</v>
+        <v>201</v>
       </c>
       <c r="F48" t="s">
-        <v>18</v>
+        <v>152</v>
       </c>
       <c r="G48" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="H48" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="I48" t="s">
-        <v>145</v>
+        <v>193</v>
       </c>
       <c r="J48">
         <v>5</v>
+      </c>
+      <c r="K48" t="s">
+        <v>194</v>
+      </c>
+      <c r="L48" t="s">
+        <v>202</v>
+      </c>
+      <c r="M48" t="s">
+        <v>199</v>
+      </c>
+      <c r="N48" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B49" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="C49" t="s">
-        <v>146</v>
+        <v>65</v>
       </c>
       <c r="D49" t="s">
-        <v>118</v>
+        <v>24</v>
       </c>
       <c r="E49" t="s">
-        <v>119</v>
+        <v>201</v>
       </c>
       <c r="F49" t="s">
-        <v>18</v>
+        <v>152</v>
       </c>
       <c r="G49" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="H49" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="I49" t="s">
-        <v>148</v>
+        <v>193</v>
       </c>
       <c r="J49">
         <v>5</v>
+      </c>
+      <c r="K49" t="s">
+        <v>155</v>
+      </c>
+      <c r="L49" t="s">
+        <v>204</v>
+      </c>
+      <c r="M49" t="s">
+        <v>199</v>
+      </c>
+      <c r="N49" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B50" t="s">
-        <v>149</v>
+        <v>14</v>
       </c>
       <c r="C50" t="s">
-        <v>197</v>
+        <v>127</v>
       </c>
       <c r="D50" t="s">
-        <v>118</v>
+        <v>16</v>
       </c>
       <c r="E50" t="s">
-        <v>192</v>
+        <v>17</v>
       </c>
       <c r="F50" t="s">
-        <v>180</v>
+        <v>18</v>
       </c>
       <c r="G50" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="H50" t="s">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="I50" t="s">
-        <v>199</v>
+        <v>129</v>
       </c>
       <c r="J50">
         <v>5</v>
-      </c>
-      <c r="K50" t="s">
-        <v>175</v>
-      </c>
-      <c r="L50" t="s">
-        <v>200</v>
-      </c>
-      <c r="M50" t="s">
-        <v>201</v>
-      </c>
-      <c r="N50" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="B51" t="s">
-        <v>149</v>
+        <v>51</v>
       </c>
       <c r="C51" t="s">
-        <v>197</v>
+        <v>131</v>
       </c>
       <c r="D51" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="E51" t="s">
-        <v>203</v>
+        <v>133</v>
       </c>
       <c r="F51" t="s">
-        <v>180</v>
+        <v>55</v>
       </c>
       <c r="G51" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="H51" t="s">
-        <v>198</v>
+        <v>135</v>
       </c>
       <c r="I51" t="s">
-        <v>204</v>
+        <v>136</v>
       </c>
       <c r="J51">
         <v>5</v>
-      </c>
-      <c r="K51" t="s">
-        <v>175</v>
-      </c>
-      <c r="L51" t="s">
-        <v>200</v>
-      </c>
-      <c r="M51" t="s">
-        <v>205</v>
-      </c>
-      <c r="N51" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="B52" t="s">
+        <v>51</v>
+      </c>
+      <c r="C52" t="s">
+        <v>131</v>
+      </c>
+      <c r="D52" t="s">
+        <v>132</v>
+      </c>
+      <c r="E52" t="s">
+        <v>133</v>
+      </c>
+      <c r="F52" t="s">
+        <v>161</v>
+      </c>
+      <c r="G52" t="s">
+        <v>134</v>
+      </c>
+      <c r="H52" t="s">
+        <v>135</v>
+      </c>
+      <c r="I52" t="s">
+        <v>136</v>
+      </c>
+      <c r="J52">
+        <v>5</v>
+      </c>
+      <c r="K52" t="s">
+        <v>155</v>
+      </c>
+      <c r="L52" t="s">
+        <v>206</v>
+      </c>
+      <c r="M52" t="s">
+        <v>207</v>
+      </c>
+      <c r="N52" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>376</v>
+      </c>
+      <c r="B53" t="s">
+        <v>14</v>
+      </c>
+      <c r="C53" t="s">
+        <v>137</v>
+      </c>
+      <c r="D53" t="s">
+        <v>90</v>
+      </c>
+      <c r="E53" t="s">
+        <v>138</v>
+      </c>
+      <c r="F53" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" t="s">
+        <v>134</v>
+      </c>
+      <c r="H53" t="s">
+        <v>31</v>
+      </c>
+      <c r="I53" t="s">
+        <v>139</v>
+      </c>
+      <c r="J53">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>376</v>
+      </c>
+      <c r="B54" t="s">
+        <v>14</v>
+      </c>
+      <c r="C54" t="s">
+        <v>137</v>
+      </c>
+      <c r="D54" t="s">
+        <v>90</v>
+      </c>
+      <c r="E54" t="s">
+        <v>140</v>
+      </c>
+      <c r="F54" t="s">
+        <v>18</v>
+      </c>
+      <c r="G54" t="s">
+        <v>134</v>
+      </c>
+      <c r="H54" t="s">
+        <v>31</v>
+      </c>
+      <c r="I54" t="s">
+        <v>139</v>
+      </c>
+      <c r="J54">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>376</v>
+      </c>
+      <c r="B55" t="s">
+        <v>14</v>
+      </c>
+      <c r="C55" t="s">
+        <v>137</v>
+      </c>
+      <c r="D55" t="s">
+        <v>90</v>
+      </c>
+      <c r="E55" t="s">
+        <v>141</v>
+      </c>
+      <c r="F55" t="s">
+        <v>18</v>
+      </c>
+      <c r="G55" t="s">
+        <v>134</v>
+      </c>
+      <c r="H55" t="s">
+        <v>31</v>
+      </c>
+      <c r="I55" t="s">
+        <v>142</v>
+      </c>
+      <c r="J55">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>376</v>
+      </c>
+      <c r="B56" t="s">
+        <v>14</v>
+      </c>
+      <c r="C56" t="s">
+        <v>137</v>
+      </c>
+      <c r="D56" t="s">
+        <v>90</v>
+      </c>
+      <c r="E56" t="s">
+        <v>143</v>
+      </c>
+      <c r="F56" t="s">
+        <v>18</v>
+      </c>
+      <c r="G56" t="s">
+        <v>134</v>
+      </c>
+      <c r="H56" t="s">
+        <v>31</v>
+      </c>
+      <c r="I56" t="s">
+        <v>144</v>
+      </c>
+      <c r="J56">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>377</v>
+      </c>
+      <c r="B57" t="s">
+        <v>22</v>
+      </c>
+      <c r="C57" t="s">
+        <v>65</v>
+      </c>
+      <c r="D57" t="s">
+        <v>115</v>
+      </c>
+      <c r="E57" t="s">
+        <v>145</v>
+      </c>
+      <c r="F57" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" t="s">
+        <v>134</v>
+      </c>
+      <c r="H57" t="s">
+        <v>27</v>
+      </c>
+      <c r="I57" t="s">
+        <v>146</v>
+      </c>
+      <c r="J57">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>377</v>
+      </c>
+      <c r="B58" t="s">
+        <v>22</v>
+      </c>
+      <c r="C58" t="s">
+        <v>65</v>
+      </c>
+      <c r="D58" t="s">
+        <v>147</v>
+      </c>
+      <c r="E58" t="s">
+        <v>148</v>
+      </c>
+      <c r="F58" t="s">
+        <v>18</v>
+      </c>
+      <c r="G58" t="s">
+        <v>134</v>
+      </c>
+      <c r="H58" t="s">
+        <v>27</v>
+      </c>
+      <c r="I58" t="s">
         <v>149</v>
       </c>
-      <c r="C52" t="s">
-        <v>197</v>
-      </c>
-      <c r="D52" t="s">
-        <v>118</v>
-      </c>
-      <c r="E52" t="s">
-        <v>119</v>
-      </c>
-      <c r="F52" t="s">
-        <v>180</v>
-      </c>
-      <c r="G52" t="s">
-        <v>147</v>
-      </c>
-      <c r="H52" t="s">
+      <c r="J58">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>377</v>
+      </c>
+      <c r="B59" t="s">
+        <v>22</v>
+      </c>
+      <c r="C59" t="s">
+        <v>65</v>
+      </c>
+      <c r="D59" t="s">
+        <v>24</v>
+      </c>
+      <c r="E59" t="s">
+        <v>209</v>
+      </c>
+      <c r="F59" t="s">
+        <v>152</v>
+      </c>
+      <c r="G59" t="s">
+        <v>134</v>
+      </c>
+      <c r="H59" t="s">
+        <v>27</v>
+      </c>
+      <c r="I59" t="s">
+        <v>210</v>
+      </c>
+      <c r="J59">
+        <v>5</v>
+      </c>
+      <c r="K59" t="s">
+        <v>194</v>
+      </c>
+      <c r="L59" t="s">
+        <v>211</v>
+      </c>
+      <c r="M59" t="s">
+        <v>199</v>
+      </c>
+      <c r="N59" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>377</v>
+      </c>
+      <c r="B60" t="s">
+        <v>22</v>
+      </c>
+      <c r="C60" t="s">
+        <v>65</v>
+      </c>
+      <c r="D60" t="s">
+        <v>24</v>
+      </c>
+      <c r="E60" t="s">
+        <v>209</v>
+      </c>
+      <c r="F60" t="s">
+        <v>152</v>
+      </c>
+      <c r="G60" t="s">
+        <v>134</v>
+      </c>
+      <c r="H60" t="s">
+        <v>27</v>
+      </c>
+      <c r="I60" t="s">
+        <v>210</v>
+      </c>
+      <c r="J60">
+        <v>5</v>
+      </c>
+      <c r="K60" t="s">
+        <v>155</v>
+      </c>
+      <c r="L60" t="s">
         <v>198</v>
       </c>
-      <c r="I52" t="s">
-        <v>207</v>
-      </c>
-      <c r="J52">
-        <v>5</v>
-      </c>
-      <c r="K52" t="s">
-        <v>175</v>
-      </c>
-      <c r="L52" t="s">
-        <v>208</v>
-      </c>
-      <c r="M52" t="s">
-        <v>209</v>
-      </c>
-      <c r="N52" t="s">
-        <v>210</v>
+      <c r="M60" t="s">
+        <v>199</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N52" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N52">
-      <sortCondition ref="A1:A52"/>
+  <autoFilter ref="A1:N60" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N60">
+      <sortCondition ref="A1:A60"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
